--- a/docs/SKN34-final-4Team_WBS.xlsx
+++ b/docs/SKN34-final-4Team_WBS.xlsx
@@ -2100,12 +2100,12 @@
       <c r="B12" s="66" t="n">
         <v>1.1</v>
       </c>
-      <c r="C12" s="67" t="inlineStr">
+      <c r="C12" s="95" t="inlineStr">
         <is>
           <t>세부 주제 탐색·제안</t>
         </is>
       </c>
-      <c r="D12" s="67" t="inlineStr">
+      <c r="D12" s="95" t="inlineStr">
         <is>
           <t>4팀 전원</t>
         </is>
@@ -2189,12 +2189,12 @@
       <c r="B13" s="66" t="n">
         <v>1.2</v>
       </c>
-      <c r="C13" s="67" t="inlineStr">
+      <c r="C13" s="95" t="inlineStr">
         <is>
           <t>1안 선정·2안 후보 준비</t>
         </is>
       </c>
-      <c r="D13" s="67" t="inlineStr">
+      <c r="D13" s="95" t="inlineStr">
         <is>
           <t>4팀 전원</t>
         </is>
@@ -2278,12 +2278,12 @@
       <c r="B14" s="66" t="n">
         <v>1.3</v>
       </c>
-      <c r="C14" s="67" t="inlineStr">
+      <c r="C14" s="95" t="inlineStr">
         <is>
           <t>1안 기획서 v1.0~v1.1 작성</t>
         </is>
       </c>
-      <c r="D14" s="67" t="inlineStr">
+      <c r="D14" s="95" t="inlineStr">
         <is>
           <t>윤성호</t>
         </is>
@@ -2367,12 +2367,12 @@
       <c r="B15" s="66" t="n">
         <v>1.4</v>
       </c>
-      <c r="C15" s="67" t="inlineStr">
+      <c r="C15" s="95" t="inlineStr">
         <is>
           <t>1회차 멘토링</t>
         </is>
       </c>
-      <c r="D15" s="67" t="inlineStr">
+      <c r="D15" s="95" t="inlineStr">
         <is>
           <t>4팀 전원</t>
         </is>
@@ -2456,12 +2456,12 @@
       <c r="B16" s="66" t="n">
         <v>1.5</v>
       </c>
-      <c r="C16" s="67" t="inlineStr">
+      <c r="C16" s="95" t="inlineStr">
         <is>
           <t>요구사항 정의서 작성</t>
         </is>
       </c>
-      <c r="D16" s="67" t="inlineStr">
+      <c r="D16" s="95" t="inlineStr">
         <is>
           <t>김기호</t>
         </is>
@@ -2545,12 +2545,12 @@
       <c r="B17" s="66" t="n">
         <v>1.6</v>
       </c>
-      <c r="C17" s="67" t="inlineStr">
+      <c r="C17" s="95" t="inlineStr">
         <is>
           <t>WBS 작성</t>
         </is>
       </c>
-      <c r="D17" s="67" t="inlineStr">
+      <c r="D17" s="95" t="inlineStr">
         <is>
           <t>정예린</t>
         </is>
@@ -2634,12 +2634,12 @@
       <c r="B18" s="66" t="n">
         <v>1.7</v>
       </c>
-      <c r="C18" s="67" t="inlineStr">
+      <c r="C18" s="95" t="inlineStr">
         <is>
           <t>기획서 최소 기준 보완·제출</t>
         </is>
       </c>
-      <c r="D18" s="67" t="inlineStr">
+      <c r="D18" s="95" t="inlineStr">
         <is>
           <t>윤성호</t>
         </is>
@@ -2723,12 +2723,12 @@
       <c r="B19" s="66" t="n">
         <v>1.8</v>
       </c>
-      <c r="C19" s="67" t="inlineStr">
+      <c r="C19" s="95" t="inlineStr">
         <is>
           <t>멘토 피드백 반영 기획 보완 ①</t>
         </is>
       </c>
-      <c r="D19" s="67" t="inlineStr">
+      <c r="D19" s="95" t="inlineStr">
         <is>
           <t>윤성호,정예린</t>
         </is>
@@ -2812,12 +2812,12 @@
       <c r="B20" s="66" t="n">
         <v>1.9</v>
       </c>
-      <c r="C20" s="67" t="inlineStr">
+      <c r="C20" s="95" t="inlineStr">
         <is>
           <t>멘토 피드백 반영 기획 보완 ②</t>
         </is>
       </c>
-      <c r="D20" s="67" t="inlineStr">
+      <c r="D20" s="95" t="inlineStr">
         <is>
           <t>정예린, 문성호</t>
         </is>
@@ -2903,12 +2903,12 @@
           <t>1.10</t>
         </is>
       </c>
-      <c r="C21" s="67" t="inlineStr">
+      <c r="C21" s="95" t="inlineStr">
         <is>
           <t>2회차 멘토링</t>
         </is>
       </c>
-      <c r="D21" s="67" t="inlineStr">
+      <c r="D21" s="95" t="inlineStr">
         <is>
           <t>4팀 전원</t>
         </is>
@@ -2992,12 +2992,12 @@
       <c r="B22" s="66" t="n">
         <v>1.11</v>
       </c>
-      <c r="C22" s="67" t="inlineStr">
+      <c r="C22" s="95" t="inlineStr">
         <is>
           <t>3회차 멘토링</t>
         </is>
       </c>
-      <c r="D22" s="67" t="inlineStr">
+      <c r="D22" s="95" t="inlineStr">
         <is>
           <t>4팀 전원</t>
         </is>
@@ -3156,12 +3156,12 @@
       <c r="B24" s="66" t="n">
         <v>2.1</v>
       </c>
-      <c r="C24" s="67" t="inlineStr">
+      <c r="C24" s="95" t="inlineStr">
         <is>
           <t>데이터 소스 확정</t>
         </is>
       </c>
-      <c r="D24" s="67" t="inlineStr">
+      <c r="D24" s="95" t="inlineStr">
         <is>
           <t>문성호, 김진화</t>
         </is>
@@ -3245,12 +3245,12 @@
       <c r="B25" s="66" t="n">
         <v>2.2</v>
       </c>
-      <c r="C25" s="67" t="inlineStr">
+      <c r="C25" s="95" t="inlineStr">
         <is>
           <t>수집 데이터 보고서 작성</t>
         </is>
       </c>
-      <c r="D25" s="67" t="inlineStr">
+      <c r="D25" s="95" t="inlineStr">
         <is>
           <t>김기호</t>
         </is>
@@ -3334,12 +3334,12 @@
       <c r="B26" s="66" t="n">
         <v>2.3</v>
       </c>
-      <c r="C26" s="67" t="inlineStr">
+      <c r="C26" s="95" t="inlineStr">
         <is>
           <t>샘플 원작 데이터 수집</t>
         </is>
       </c>
-      <c r="D26" s="67" t="inlineStr">
+      <c r="D26" s="95" t="inlineStr">
         <is>
           <t>김진화, 문성호</t>
         </is>
@@ -3423,12 +3423,12 @@
       <c r="B27" s="66" t="n">
         <v>2.4</v>
       </c>
-      <c r="C27" s="67" t="inlineStr">
+      <c r="C27" s="95" t="inlineStr">
         <is>
           <t>가상 독자 피드백 데이터 제작</t>
         </is>
       </c>
-      <c r="D27" s="67" t="inlineStr">
+      <c r="D27" s="95" t="inlineStr">
         <is>
           <t>김진화, 문성호</t>
         </is>
@@ -3512,12 +3512,12 @@
       <c r="B28" s="66" t="n">
         <v>2.5</v>
       </c>
-      <c r="C28" s="67" t="inlineStr">
+      <c r="C28" s="95" t="inlineStr">
         <is>
           <t>DB 테이블 설계</t>
         </is>
       </c>
-      <c r="D28" s="67" t="inlineStr">
+      <c r="D28" s="95" t="inlineStr">
         <is>
           <t>정예린, 윤성호</t>
         </is>
@@ -3601,12 +3601,12 @@
       <c r="B29" s="66" t="n">
         <v>2.6</v>
       </c>
-      <c r="C29" s="67" t="inlineStr">
+      <c r="C29" s="95" t="inlineStr">
         <is>
           <t>DB 구축·데이터 적재</t>
         </is>
       </c>
-      <c r="D29" s="67" t="inlineStr">
+      <c r="D29" s="95" t="inlineStr">
         <is>
           <t>윤성호</t>
         </is>
@@ -3690,12 +3690,12 @@
       <c r="B30" s="66" t="n">
         <v>2.7</v>
       </c>
-      <c r="C30" s="67" t="inlineStr">
+      <c r="C30" s="95" t="inlineStr">
         <is>
           <t>데이터베이스/저장소 설계 문서 작성</t>
         </is>
       </c>
-      <c r="D30" s="67" t="inlineStr">
+      <c r="D30" s="95" t="inlineStr">
         <is>
           <t>정예린</t>
         </is>
@@ -3856,12 +3856,12 @@
       <c r="B32" s="66" t="n">
         <v>3.1</v>
       </c>
-      <c r="C32" s="67" t="inlineStr">
+      <c r="C32" s="95" t="inlineStr">
         <is>
           <t>원고 전처리</t>
         </is>
       </c>
-      <c r="D32" s="67" t="inlineStr">
+      <c r="D32" s="95" t="inlineStr">
         <is>
           <t>문성호</t>
         </is>
@@ -3945,12 +3945,12 @@
       <c r="B33" s="66" t="n">
         <v>3.2</v>
       </c>
-      <c r="C33" s="67" t="inlineStr">
+      <c r="C33" s="95" t="inlineStr">
         <is>
           <t>피드백 라벨링 기준 확정</t>
         </is>
       </c>
-      <c r="D33" s="67" t="inlineStr">
+      <c r="D33" s="95" t="inlineStr">
         <is>
           <t>문성호</t>
         </is>
@@ -4034,12 +4034,12 @@
       <c r="B34" s="66" t="n">
         <v>3.3</v>
       </c>
-      <c r="C34" s="67" t="inlineStr">
+      <c r="C34" s="95" t="inlineStr">
         <is>
           <t>피드백 라벨링</t>
         </is>
       </c>
-      <c r="D34" s="67" t="inlineStr">
+      <c r="D34" s="95" t="inlineStr">
         <is>
           <t>김진화, 김기호</t>
         </is>
@@ -4123,12 +4123,12 @@
       <c r="B35" s="66" t="n">
         <v>3.4</v>
       </c>
-      <c r="C35" s="67" t="inlineStr">
+      <c r="C35" s="95" t="inlineStr">
         <is>
           <t>데이터 전처리 결과서 작성</t>
         </is>
       </c>
-      <c r="D35" s="67" t="inlineStr">
+      <c r="D35" s="95" t="inlineStr">
         <is>
           <t>문성호</t>
         </is>
@@ -4212,12 +4212,12 @@
       <c r="B36" s="66" t="n">
         <v>3.5</v>
       </c>
-      <c r="C36" s="67" t="inlineStr">
+      <c r="C36" s="95" t="inlineStr">
         <is>
           <t>ML/DL 분류 모델 학습</t>
         </is>
       </c>
-      <c r="D36" s="67" t="inlineStr">
+      <c r="D36" s="95" t="inlineStr">
         <is>
           <t>문성호</t>
         </is>
@@ -4301,12 +4301,12 @@
       <c r="B37" s="66" t="n">
         <v>3.6</v>
       </c>
-      <c r="C37" s="67" t="inlineStr">
+      <c r="C37" s="95" t="inlineStr">
         <is>
           <t>모델 평가·튜닝</t>
         </is>
       </c>
-      <c r="D37" s="67" t="inlineStr">
+      <c r="D37" s="95" t="inlineStr">
         <is>
           <t>문성호</t>
         </is>
@@ -4390,12 +4390,12 @@
       <c r="B38" s="66" t="n">
         <v>3.7</v>
       </c>
-      <c r="C38" s="67" t="inlineStr">
+      <c r="C38" s="95" t="inlineStr">
         <is>
           <t>ML/DL 학습결과서 작성</t>
         </is>
       </c>
-      <c r="D38" s="67" t="inlineStr">
+      <c r="D38" s="95" t="inlineStr">
         <is>
           <t>정예린, 문성호</t>
         </is>
@@ -4556,12 +4556,12 @@
       <c r="B40" s="66" t="n">
         <v>4.1</v>
       </c>
-      <c r="C40" s="67" t="inlineStr">
+      <c r="C40" s="95" t="inlineStr">
         <is>
           <t>AI 시스템 아키텍처 설계</t>
         </is>
       </c>
-      <c r="D40" s="67" t="inlineStr">
+      <c r="D40" s="95" t="inlineStr">
         <is>
           <t>김기호, 윤성호</t>
         </is>
@@ -4645,12 +4645,12 @@
       <c r="B41" s="66" t="n">
         <v>4.2</v>
       </c>
-      <c r="C41" s="67" t="inlineStr">
+      <c r="C41" s="95" t="inlineStr">
         <is>
           <t>AI 시스템 아키텍처 문서 작성</t>
         </is>
       </c>
-      <c r="D41" s="67" t="inlineStr">
+      <c r="D41" s="95" t="inlineStr">
         <is>
           <t>김기호</t>
         </is>
@@ -4734,12 +4734,12 @@
       <c r="B42" s="66" t="n">
         <v>4.3</v>
       </c>
-      <c r="C42" s="67" t="inlineStr">
+      <c r="C42" s="95" t="inlineStr">
         <is>
           <t>벡터DB 구축</t>
         </is>
       </c>
-      <c r="D42" s="67" t="inlineStr">
+      <c r="D42" s="95" t="inlineStr">
         <is>
           <t>김기호</t>
         </is>
@@ -4823,12 +4823,12 @@
       <c r="B43" s="66" t="n">
         <v>4.4</v>
       </c>
-      <c r="C43" s="67" t="inlineStr">
+      <c r="C43" s="95" t="inlineStr">
         <is>
           <t>RAG 검색 테스트</t>
         </is>
       </c>
-      <c r="D43" s="67" t="inlineStr">
+      <c r="D43" s="95" t="inlineStr">
         <is>
           <t>김기호</t>
         </is>
@@ -4912,12 +4912,12 @@
       <c r="B44" s="66" t="n">
         <v>4.5</v>
       </c>
-      <c r="C44" s="67" t="inlineStr">
+      <c r="C44" s="95" t="inlineStr">
         <is>
           <t>벡터DB/GraphDB 구축 결과서 작성</t>
         </is>
       </c>
-      <c r="D44" s="67" t="inlineStr">
+      <c r="D44" s="95" t="inlineStr">
         <is>
           <t>김진화, 김기호</t>
         </is>
@@ -5001,12 +5001,12 @@
       <c r="B45" s="66" t="n">
         <v>4.6</v>
       </c>
-      <c r="C45" s="67" t="inlineStr">
+      <c r="C45" s="95" t="inlineStr">
         <is>
           <t>피드백 분석·응대 에이전트 개발</t>
         </is>
       </c>
-      <c r="D45" s="67" t="inlineStr">
+      <c r="D45" s="95" t="inlineStr">
         <is>
           <t>김기호</t>
         </is>
@@ -5090,12 +5090,12 @@
       <c r="B46" s="66" t="n">
         <v>4.7</v>
       </c>
-      <c r="C46" s="67" t="inlineStr">
+      <c r="C46" s="95" t="inlineStr">
         <is>
           <t>설정 검토 에이전트 개발</t>
         </is>
       </c>
-      <c r="D46" s="67" t="inlineStr">
+      <c r="D46" s="95" t="inlineStr">
         <is>
           <t>문성호</t>
         </is>
@@ -5179,12 +5179,12 @@
       <c r="B47" s="66" t="n">
         <v>4.8</v>
       </c>
-      <c r="C47" s="67" t="inlineStr">
+      <c r="C47" s="95" t="inlineStr">
         <is>
           <t>인물·스토리 계획 에이전트 개발</t>
         </is>
       </c>
-      <c r="D47" s="67" t="inlineStr">
+      <c r="D47" s="95" t="inlineStr">
         <is>
           <t>문성호</t>
         </is>
@@ -5268,12 +5268,12 @@
       <c r="B48" s="66" t="n">
         <v>4.9</v>
       </c>
-      <c r="C48" s="67" t="inlineStr">
+      <c r="C48" s="95" t="inlineStr">
         <is>
           <t>LLM 활용 소프트웨어 통합</t>
         </is>
       </c>
-      <c r="D48" s="67" t="inlineStr">
+      <c r="D48" s="95" t="inlineStr">
         <is>
           <t>김기호, 윤성호</t>
         </is>
@@ -5359,12 +5359,12 @@
           <t>4.10</t>
         </is>
       </c>
-      <c r="C49" s="67" t="inlineStr">
+      <c r="C49" s="95" t="inlineStr">
         <is>
           <t>멀티 에이전트 테스트 계획 수립</t>
         </is>
       </c>
-      <c r="D49" s="67" t="inlineStr">
+      <c r="D49" s="95" t="inlineStr">
         <is>
           <t>김진화</t>
         </is>
@@ -5448,12 +5448,12 @@
       <c r="B50" s="66" t="n">
         <v>4.11</v>
       </c>
-      <c r="C50" s="67" t="inlineStr">
+      <c r="C50" s="95" t="inlineStr">
         <is>
           <t>멀티 에이전트 테스트 수행·개선</t>
         </is>
       </c>
-      <c r="D50" s="67" t="inlineStr">
+      <c r="D50" s="95" t="inlineStr">
         <is>
           <t>김진화, 문성호</t>
         </is>
@@ -5537,12 +5537,12 @@
       <c r="B51" s="66" t="n">
         <v>4.12</v>
       </c>
-      <c r="C51" s="67" t="inlineStr">
+      <c r="C51" s="95" t="inlineStr">
         <is>
           <t>멀티 에이전트 테스트 계획·결과 보고서 작성</t>
         </is>
       </c>
-      <c r="D51" s="67" t="inlineStr">
+      <c r="D51" s="95" t="inlineStr">
         <is>
           <t>정예린, 김진화</t>
         </is>
@@ -5703,12 +5703,12 @@
       <c r="B53" s="66" t="n">
         <v>5.1</v>
       </c>
-      <c r="C53" s="67" t="inlineStr">
+      <c r="C53" s="95" t="inlineStr">
         <is>
           <t>화면 흐름 설계</t>
         </is>
       </c>
-      <c r="D53" s="67" t="inlineStr">
+      <c r="D53" s="95" t="inlineStr">
         <is>
           <t>정예린</t>
         </is>
@@ -5792,12 +5792,12 @@
       <c r="B54" s="66" t="n">
         <v>5.2</v>
       </c>
-      <c r="C54" s="67" t="inlineStr">
+      <c r="C54" s="95" t="inlineStr">
         <is>
           <t>화면설계서 작성</t>
         </is>
       </c>
-      <c r="D54" s="67" t="inlineStr">
+      <c r="D54" s="95" t="inlineStr">
         <is>
           <t>정예린</t>
         </is>
@@ -5881,12 +5881,12 @@
       <c r="B55" s="66" t="n">
         <v>5.3</v>
       </c>
-      <c r="C55" s="67" t="inlineStr">
+      <c r="C55" s="95" t="inlineStr">
         <is>
           <t>시스템 구성도 작성</t>
         </is>
       </c>
-      <c r="D55" s="67" t="inlineStr">
+      <c r="D55" s="95" t="inlineStr">
         <is>
           <t>윤성호</t>
         </is>
@@ -5970,12 +5970,12 @@
       <c r="B56" s="66" t="n">
         <v>5.4</v>
       </c>
-      <c r="C56" s="67" t="inlineStr">
+      <c r="C56" s="95" t="inlineStr">
         <is>
           <t>프론트엔드: 공통 레이아웃</t>
         </is>
       </c>
-      <c r="D56" s="67" t="inlineStr">
+      <c r="D56" s="95" t="inlineStr">
         <is>
           <t>김진화</t>
         </is>
@@ -6059,12 +6059,12 @@
       <c r="B57" s="66" t="n">
         <v>5.5</v>
       </c>
-      <c r="C57" s="67" t="inlineStr">
+      <c r="C57" s="95" t="inlineStr">
         <is>
           <t>프론트엔드: 독자 화면(열람·피드백·Fork)</t>
         </is>
       </c>
-      <c r="D57" s="67" t="inlineStr">
+      <c r="D57" s="95" t="inlineStr">
         <is>
           <t>김진화</t>
         </is>
@@ -6148,12 +6148,12 @@
       <c r="B58" s="66" t="n">
         <v>5.6</v>
       </c>
-      <c r="C58" s="67" t="inlineStr">
+      <c r="C58" s="95" t="inlineStr">
         <is>
           <t>프론트엔드: 작가·운영자 화면(PR 검토·피드백 관리·실패 경고·신고 처리)</t>
         </is>
       </c>
-      <c r="D58" s="67" t="inlineStr">
+      <c r="D58" s="95" t="inlineStr">
         <is>
           <t>김진화</t>
         </is>
@@ -6237,12 +6237,12 @@
       <c r="B59" s="66" t="n">
         <v>5.7</v>
       </c>
-      <c r="C59" s="67" t="inlineStr">
+      <c r="C59" s="95" t="inlineStr">
         <is>
           <t>백엔드: API 설계·인증</t>
         </is>
       </c>
-      <c r="D59" s="67" t="inlineStr">
+      <c r="D59" s="95" t="inlineStr">
         <is>
           <t>윤성호</t>
         </is>
@@ -6326,12 +6326,12 @@
       <c r="B60" s="66" t="n">
         <v>5.8</v>
       </c>
-      <c r="C60" s="67" t="inlineStr">
+      <c r="C60" s="95" t="inlineStr">
         <is>
           <t>백엔드: 피드백·PR·Fork API</t>
         </is>
       </c>
-      <c r="D60" s="67" t="inlineStr">
+      <c r="D60" s="95" t="inlineStr">
         <is>
           <t>윤성호</t>
         </is>
@@ -6415,12 +6415,12 @@
       <c r="B61" s="66" t="n">
         <v>5.9</v>
       </c>
-      <c r="C61" s="67" t="inlineStr">
+      <c r="C61" s="95" t="inlineStr">
         <is>
           <t>LLM 연동 웹 앱 통합</t>
         </is>
       </c>
-      <c r="D61" s="67" t="inlineStr">
+      <c r="D61" s="95" t="inlineStr">
         <is>
           <t>윤성호, 김기호</t>
         </is>
@@ -6506,12 +6506,12 @@
           <t>5.10</t>
         </is>
       </c>
-      <c r="C62" s="67" t="inlineStr">
+      <c r="C62" s="95" t="inlineStr">
         <is>
           <t>통합 연동 테스트·수정</t>
         </is>
       </c>
-      <c r="D62" s="67" t="inlineStr">
+      <c r="D62" s="95" t="inlineStr">
         <is>
           <t>윤성호, 김기호</t>
         </is>
@@ -6595,12 +6595,12 @@
       <c r="B63" s="66" t="n">
         <v>5.11</v>
       </c>
-      <c r="C63" s="67" t="inlineStr">
+      <c r="C63" s="95" t="inlineStr">
         <is>
           <t>서비스 테스트 계획 수립</t>
         </is>
       </c>
-      <c r="D63" s="67" t="inlineStr">
+      <c r="D63" s="95" t="inlineStr">
         <is>
           <t>김진화</t>
         </is>
@@ -6684,12 +6684,12 @@
       <c r="B64" s="66" t="n">
         <v>5.12</v>
       </c>
-      <c r="C64" s="67" t="inlineStr">
+      <c r="C64" s="95" t="inlineStr">
         <is>
           <t>서비스 테스트 수행·버그 수정</t>
         </is>
       </c>
-      <c r="D64" s="67" t="inlineStr">
+      <c r="D64" s="95" t="inlineStr">
         <is>
           <t>4팀 전원</t>
         </is>
@@ -6773,12 +6773,12 @@
       <c r="B65" s="66" t="n">
         <v>5.13</v>
       </c>
-      <c r="C65" s="67" t="inlineStr">
+      <c r="C65" s="95" t="inlineStr">
         <is>
           <t>서비스 테스트 계획·결과 보고서 작성</t>
         </is>
       </c>
-      <c r="D65" s="67" t="inlineStr">
+      <c r="D65" s="95" t="inlineStr">
         <is>
           <t>김진화</t>
         </is>
@@ -6941,12 +6941,12 @@
           <t>6.10</t>
         </is>
       </c>
-      <c r="C67" s="67" t="inlineStr">
+      <c r="C67" s="95" t="inlineStr">
         <is>
           <t>중간발표 PT 작성</t>
         </is>
       </c>
-      <c r="D67" s="67" t="inlineStr">
+      <c r="D67" s="95" t="inlineStr">
         <is>
           <t>정예린, 윤성호</t>
         </is>
@@ -7030,12 +7030,12 @@
       <c r="B68" s="66" t="n">
         <v>6.2</v>
       </c>
-      <c r="C68" s="67" t="inlineStr">
+      <c r="C68" s="95" t="inlineStr">
         <is>
           <t>중간발표 리허설</t>
         </is>
       </c>
-      <c r="D68" s="67" t="inlineStr">
+      <c r="D68" s="95" t="inlineStr">
         <is>
           <t>4팀 전원</t>
         </is>
@@ -7119,12 +7119,12 @@
       <c r="B69" s="66" t="n">
         <v>6.3</v>
       </c>
-      <c r="C69" s="67" t="inlineStr">
+      <c r="C69" s="95" t="inlineStr">
         <is>
           <t>중간발표</t>
         </is>
       </c>
-      <c r="D69" s="67" t="inlineStr">
+      <c r="D69" s="95" t="inlineStr">
         <is>
           <t>윤성호</t>
         </is>
@@ -7208,12 +7208,12 @@
       <c r="B70" s="66" t="n">
         <v>6.4</v>
       </c>
-      <c r="C70" s="67" t="inlineStr">
+      <c r="C70" s="95" t="inlineStr">
         <is>
           <t>최종발표 PT 작성</t>
         </is>
       </c>
-      <c r="D70" s="67" t="inlineStr">
+      <c r="D70" s="95" t="inlineStr">
         <is>
           <t>정예린, 윤성호, 문성호</t>
         </is>
@@ -7297,12 +7297,12 @@
       <c r="B71" s="66" t="n">
         <v>6.5</v>
       </c>
-      <c r="C71" s="67" t="inlineStr">
+      <c r="C71" s="95" t="inlineStr">
         <is>
           <t>시연영상 제작</t>
         </is>
       </c>
-      <c r="D71" s="67" t="inlineStr">
+      <c r="D71" s="95" t="inlineStr">
         <is>
           <t>김진화, 김기호</t>
         </is>
@@ -7386,12 +7386,12 @@
       <c r="B72" s="66" t="n">
         <v>6.6</v>
       </c>
-      <c r="C72" s="67" t="inlineStr">
+      <c r="C72" s="95" t="inlineStr">
         <is>
           <t>소스코드 정리·제출</t>
         </is>
       </c>
-      <c r="D72" s="67" t="inlineStr">
+      <c r="D72" s="95" t="inlineStr">
         <is>
           <t>김기호, 윤성호</t>
         </is>
@@ -7475,12 +7475,12 @@
       <c r="B73" s="66" t="n">
         <v>6.7</v>
       </c>
-      <c r="C73" s="67" t="inlineStr">
+      <c r="C73" s="95" t="inlineStr">
         <is>
           <t>최종발표</t>
         </is>
       </c>
-      <c r="D73" s="67" t="inlineStr">
+      <c r="D73" s="95" t="inlineStr">
         <is>
           <t>윤성호</t>
         </is>
@@ -7643,12 +7643,12 @@
           <t>7.10</t>
         </is>
       </c>
-      <c r="C75" s="67" t="inlineStr">
+      <c r="C75" s="95" t="inlineStr">
         <is>
           <t>강사님 주간 공유</t>
         </is>
       </c>
-      <c r="D75" s="67" t="inlineStr">
+      <c r="D75" s="95" t="inlineStr">
         <is>
           <t>정예린</t>
         </is>
@@ -7732,12 +7732,12 @@
       <c r="B76" s="66" t="n">
         <v>7.2</v>
       </c>
-      <c r="C76" s="67" t="inlineStr">
+      <c r="C76" s="95" t="inlineStr">
         <is>
           <t>주간업무일지 작성</t>
         </is>
       </c>
-      <c r="D76" s="67" t="inlineStr">
+      <c r="D76" s="95" t="inlineStr">
         <is>
           <t>정예린</t>
         </is>
@@ -7821,12 +7821,12 @@
       <c r="B77" s="66" t="n">
         <v>7.3</v>
       </c>
-      <c r="C77" s="67" t="inlineStr">
+      <c r="C77" s="95" t="inlineStr">
         <is>
           <t>주간 스탠드업</t>
         </is>
       </c>
-      <c r="D77" s="67" t="inlineStr">
+      <c r="D77" s="95" t="inlineStr">
         <is>
           <t>4팀 전원</t>
         </is>
@@ -8893,7 +8893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="24"/>
   <cols>
     <col width="17" customWidth="1" style="83" min="1" max="1"/>
@@ -8921,7 +8921,7 @@
       <c r="H1" s="94" t="n"/>
     </row>
     <row r="2" ht="42" customHeight="1" s="83">
-      <c r="A2" s="67" t="inlineStr">
+      <c r="A2" s="95" t="inlineStr">
         <is>
           <t>2026-10-27 저장소 확인 기준. 원본 간트의 담당자·일정·기간·완료율은 그대로 보존했습니다. 아래 현황은 실행 재검증이나 팀 외부 작업 확인을 대신하지 않습니다.</t>
         </is>
@@ -8977,714 +8977,714 @@
       </c>
     </row>
     <row r="4" ht="44" customHeight="1" s="83">
-      <c r="A4" s="67" t="inlineStr">
+      <c r="A4" s="95" t="inlineStr">
         <is>
           <t>BASE-01</t>
         </is>
       </c>
-      <c r="B4" s="67" t="inlineStr">
+      <c r="B4" s="95" t="inlineStr">
         <is>
           <t>개발 기반 / 기존 WBS 명시 없음</t>
         </is>
       </c>
-      <c r="C4" s="67" t="inlineStr">
+      <c r="C4" s="95" t="inlineStr">
         <is>
           <t>3서비스·시작 화면·Health</t>
         </is>
       </c>
-      <c r="D4" s="67" t="inlineStr">
+      <c r="D4" s="95" t="inlineStr">
         <is>
           <t>코드 구현 확인 / 실행 재검증 안함</t>
         </is>
       </c>
-      <c r="E4" s="67" t="inlineStr">
+      <c r="E4" s="95" t="inlineStr">
         <is>
           <t>4ea0526: React 시작 화면, Core Health 및 AI Health 중계, FastAPI 내부 Health, dev/prod Compose.</t>
         </is>
       </c>
-      <c r="F4" s="67" t="inlineStr">
+      <c r="F4" s="95" t="inlineStr">
         <is>
           <t>업무 CRUD·인증·DB·모델 호출은 없음. 인터넷 운영 배포 완료를 뜻하지 않음.</t>
         </is>
       </c>
-      <c r="G4" s="67" t="inlineStr">
+      <c r="G4" s="95" t="inlineStr">
         <is>
           <t>별도 기반 작업으로 편입 여부 검토. 기존 5.4·5.7·5.9 완료율에 합산하지 않음.</t>
         </is>
       </c>
-      <c r="H4" s="67" t="inlineStr">
+      <c r="H4" s="95" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" s="83">
-      <c r="A5" s="67" t="inlineStr">
+      <c r="A5" s="95" t="inlineStr">
         <is>
           <t>BASE-02</t>
         </is>
       </c>
-      <c r="B5" s="67" t="inlineStr">
+      <c r="B5" s="95" t="inlineStr">
         <is>
           <t>4.1·4.2·5.3 관련</t>
         </is>
       </c>
-      <c r="C5" s="67" t="inlineStr">
+      <c r="C5" s="95" t="inlineStr">
         <is>
           <t>현행 아키텍처·서비스 책임</t>
         </is>
       </c>
-      <c r="D5" s="67" t="inlineStr">
+      <c r="D5" s="95" t="inlineStr">
         <is>
           <t>문서 존재 / AI 상세 설계 미완료</t>
         </is>
       </c>
-      <c r="E5" s="67" t="inlineStr">
+      <c r="E5" s="95" t="inlineStr">
         <is>
           <t>architecture.md; ../AGENTS.md; ../backend/ai-service/docs/agent-structure.md</t>
         </is>
       </c>
-      <c r="F5" s="67" t="inlineStr">
+      <c r="F5" s="95" t="inlineStr">
         <is>
           <t>현행 3서비스 연결·책임 설명은 있음. AI 업무 입출력·에이전트 계약·목표 구성도 완료 근거는 아님.</t>
         </is>
       </c>
-      <c r="G5" s="67" t="inlineStr">
+      <c r="G5" s="95" t="inlineStr">
         <is>
           <t>기존 설계 문서 재사용. 4.1·4.2·5.3의 완료 기준 확인 후 일정·진척 갱신.</t>
         </is>
       </c>
-      <c r="H5" s="67" t="inlineStr">
+      <c r="H5" s="95" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" s="83">
-      <c r="A6" s="67" t="inlineStr">
+      <c r="A6" s="95" t="inlineStr">
         <is>
           <t>DOC-01</t>
         </is>
       </c>
-      <c r="B6" s="67" t="inlineStr">
+      <c r="B6" s="95" t="inlineStr">
         <is>
           <t>1.5·5.1 관련</t>
         </is>
       </c>
-      <c r="C6" s="67" t="inlineStr">
+      <c r="C6" s="95" t="inlineStr">
         <is>
           <t>액터·유스케이스·UC별 명세</t>
         </is>
       </c>
-      <c r="D6" s="67" t="inlineStr">
-        <is>
-          <t>v3 작성 / 일부 정책 미확정</t>
-        </is>
-      </c>
-      <c r="E6" s="67" t="inlineStr">
-        <is>
-          <t>docs/usecase.md v3, docs/usecase-spec/UC-01~24.md. 세계관·작품 분리, 자율 연재 자동 발행, 크레딧 부담 주체 등 팀 결정 반영.</t>
-        </is>
-      </c>
-      <c r="F6" s="67" t="inlineStr">
+      <c r="D6" s="95" t="inlineStr">
+        <is>
+          <t>v5 작성 / 일부 정책 미확정</t>
+        </is>
+      </c>
+      <c r="E6" s="95" t="inlineStr">
+        <is>
+          <t>docs/usecase.md v5, docs/usecase-spec/UC-01~25.md. 세계관·작품 분리, 세계관 버전·세계관 Fork, 자율 연재 자동 발행, 크레딧 부담 주체 등 팀 결정 반영.</t>
+        </is>
+      </c>
+      <c r="F6" s="95" t="inlineStr">
         <is>
           <t>요구사항 상세 승인·화면설계 완료와 다름. 개발 범위를 자동 확정하지 않음.</t>
         </is>
       </c>
-      <c r="G6" s="67" t="inlineStr">
+      <c r="G6" s="95" t="inlineStr">
         <is>
           <t>확정 정책 기준으로 화면 흐름(5.1)·DB 설계(2.5) 착수, 남은 미정 사항 합의.</t>
         </is>
       </c>
-      <c r="H6" s="67" t="inlineStr">
+      <c r="H6" s="95" t="inlineStr">
+        <is>
+          <t>usecase v5 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1" s="83">
+      <c r="A7" s="95" t="inlineStr">
+        <is>
+          <t>DOC-02</t>
+        </is>
+      </c>
+      <c r="B7" s="95" t="inlineStr">
+        <is>
+          <t>1.5·1.6 / 이번 문서 정리</t>
+        </is>
+      </c>
+      <c r="C7" s="95" t="inlineStr">
+        <is>
+          <t>요구사항·WBS 기준 정합화</t>
+        </is>
+      </c>
+      <c r="D7" s="95" t="inlineStr">
+        <is>
+          <t>이번 반영 / 기능 개발 아님</t>
+        </is>
+      </c>
+      <c r="E7" s="95" t="inlineStr">
+        <is>
+          <t>요구사항 80개 ID 유지, UC·명세·구현·관련 WBS 열 및 정리 기준 추가. WBS 원본 간트 보존.</t>
+        </is>
+      </c>
+      <c r="F7" s="95" t="inlineStr">
+        <is>
+          <t>원본 완료 15개·0% 44개·미입력 1개는 팀 기록이며 이번에 실제 완료를 재검증한 수치가 아님.</t>
+        </is>
+      </c>
+      <c r="G7" s="95" t="inlineStr">
+        <is>
+          <t>향후 완료 보고에는 기능 ID·관련 WBS·검증 근거를 함께 남김.</t>
+        </is>
+      </c>
+      <c r="H7" s="95" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1" s="83">
+      <c r="A8" s="95" t="inlineStr">
+        <is>
+          <t>CHECK-01</t>
+        </is>
+      </c>
+      <c r="B8" s="95" t="inlineStr">
+        <is>
+          <t>1.1~1.10·2.1·2.2·7.10·7.2·7.3</t>
+        </is>
+      </c>
+      <c r="C8" s="95" t="inlineStr">
+        <is>
+          <t>기존 완료 표시</t>
+        </is>
+      </c>
+      <c r="D8" s="95" t="inlineStr">
+        <is>
+          <t>기존 기록 보존 / 재검증 안함</t>
+        </is>
+      </c>
+      <c r="E8" s="95" t="inlineStr">
+        <is>
+          <t>원본 갠트 H열 100% 15개. 산출물·회의·수집 완료 여부를 이번에 전부 확인하지 않음.</t>
+        </is>
+      </c>
+      <c r="F8" s="95" t="inlineStr">
+        <is>
+          <t>날짜가 지났거나 완료율이 기록되어 있다는 이유만으로 완료 근거를 만들지 않음.</t>
+        </is>
+      </c>
+      <c r="G8" s="95" t="inlineStr">
+        <is>
+          <t>담당자·산출물 확인이 필요한 시점에 원본 값을 갱신.</t>
+        </is>
+      </c>
+      <c r="H8" s="95" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" s="83">
+      <c r="A9" s="95" t="inlineStr">
+        <is>
+          <t>CHECK-02</t>
+        </is>
+      </c>
+      <c r="B9" s="95" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="C9" s="95" t="inlineStr">
+        <is>
+          <t>3회차 멘토링</t>
+        </is>
+      </c>
+      <c r="D9" s="95" t="inlineStr">
+        <is>
+          <t>완료율 미입력 / 원본 보존</t>
+        </is>
+      </c>
+      <c r="E9" s="95" t="inlineStr">
+        <is>
+          <t>원본 일정 2026-10-29, 완료율 공란.</t>
+        </is>
+      </c>
+      <c r="F9" s="95" t="inlineStr">
+        <is>
+          <t>공란을 0% 또는 완료로 자동 변환하지 않음.</t>
+        </is>
+      </c>
+      <c r="G9" s="95" t="inlineStr">
+        <is>
+          <t>실제 진행 후 담당자가 기록.</t>
+        </is>
+      </c>
+      <c r="H9" s="95" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1" s="83">
+      <c r="A10" s="95" t="inlineStr">
+        <is>
+          <t>CHECK-03</t>
+        </is>
+      </c>
+      <c r="B10" s="95" t="inlineStr">
+        <is>
+          <t>2.3·2.4·3.1~3.7·4.3~4.5</t>
+        </is>
+      </c>
+      <c r="C10" s="95" t="inlineStr">
+        <is>
+          <t>데이터·학습·검색 작업</t>
+        </is>
+      </c>
+      <c r="D10" s="95" t="inlineStr">
+        <is>
+          <t>기존 0% 보존 / 진행 별도 확인</t>
+        </is>
+      </c>
+      <c r="E10" s="95" t="inlineStr">
+        <is>
+          <t>기획 후보와 원본 일정은 존재. 외부 작업·데이터 수집·학습 결과는 이번 검토 범위에서 확인하지 않음.</t>
+        </is>
+      </c>
+      <c r="F10" s="95" t="inlineStr">
+        <is>
+          <t>저장소 부재만으로 팀의 외부 작업 부재를 단정하지 않음. 데이터 이용 조건·평가 목적 확인 필요.</t>
+        </is>
+      </c>
+      <c r="G10" s="95" t="inlineStr">
+        <is>
+          <t>담당자 산출물 확인 전 진행률 임의 변경 금지. 모델·벡터DB는 기존 계획이며 채택 검증과 구분.</t>
+        </is>
+      </c>
+      <c r="H10" s="95" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="44" customHeight="1" s="83">
+      <c r="A11" s="95" t="inlineStr">
+        <is>
+          <t>DEV-01</t>
+        </is>
+      </c>
+      <c r="B11" s="95" t="inlineStr">
+        <is>
+          <t>2.5·2.6·5.7</t>
+        </is>
+      </c>
+      <c r="C11" s="95" t="inlineStr">
+        <is>
+          <t>데이터 기반·인증</t>
+        </is>
+      </c>
+      <c r="D11" s="95" t="inlineStr">
+        <is>
+          <t>업무 구현 없음 / 계약 미정</t>
+        </is>
+      </c>
+      <c r="E11" s="95" t="inlineStr">
+        <is>
+          <t>../README.md; 현재 Core 소스는 Health만 존재. F-ACT·F-OPS 관련.</t>
+        </is>
+      </c>
+      <c r="F11" s="95" t="inlineStr">
+        <is>
+          <t>DB·인증 방식·권한·계정 수명주기 미정. 현행 저장소에 DB·로그인 없음.</t>
+        </is>
+      </c>
+      <c r="G11" s="95" t="inlineStr">
+        <is>
+          <t>착수 기능의 권한·저장 범위를 합의한 뒤 DB·API·화면 계약 구체화.</t>
+        </is>
+      </c>
+      <c r="H11" s="95" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1" s="83">
+      <c r="A12" s="95" t="inlineStr">
+        <is>
+          <t>DEV-02</t>
+        </is>
+      </c>
+      <c r="B12" s="95" t="inlineStr">
+        <is>
+          <t>4.6~4.9·5.9</t>
+        </is>
+      </c>
+      <c r="C12" s="95" t="inlineStr">
+        <is>
+          <t>AI 업무·LLM 연동</t>
+        </is>
+      </c>
+      <c r="D12" s="95" t="inlineStr">
+        <is>
+          <t>미구현</t>
+        </is>
+      </c>
+      <c r="E12" s="95" t="inlineStr">
+        <is>
+          <t>../backend/ai-service/app/main.py; health/router.py. 실행 Agent·모델 호출 없음.</t>
+        </is>
+      </c>
+      <c r="F12" s="95" t="inlineStr">
+        <is>
+          <t>OpenAI Agents SDK 의존성이나 Health 연결은 생성 기능 완료 증거가 아님.</t>
+        </is>
+      </c>
+      <c r="G12" s="95" t="inlineStr">
+        <is>
+          <t>AI 입력·출력·허용 문맥과 실패 처리 계약을 정한 기능부터 구현.</t>
+        </is>
+      </c>
+      <c r="H12" s="95" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="44" customHeight="1" s="83">
+      <c r="A13" s="95" t="inlineStr">
+        <is>
+          <t>DEV-03</t>
+        </is>
+      </c>
+      <c r="B13" s="95" t="inlineStr">
+        <is>
+          <t>5.4~5.8</t>
+        </is>
+      </c>
+      <c r="C13" s="95" t="inlineStr">
+        <is>
+          <t>서비스 화면·업무 API</t>
+        </is>
+      </c>
+      <c r="D13" s="95" t="inlineStr">
+        <is>
+          <t>미구현 / 시작 화면만 존재</t>
+        </is>
+      </c>
+      <c r="E13" s="95" t="inlineStr">
+        <is>
+          <t>../frontend/src/App.tsx; Core Health Controller 2개. 요구사항 80개 전부 미구현.</t>
+        </is>
+      </c>
+      <c r="F13" s="95" t="inlineStr">
+        <is>
+          <t>시작 화면을 공통 업무 레이아웃·독자/작가 화면·인증/Fork API 완료로 계산하지 않음.</t>
+        </is>
+      </c>
+      <c r="G13" s="95" t="inlineStr">
+        <is>
+          <t>선택 기능 단위로 관련 요구사항과 화면·API·수용 기준 연결.</t>
+        </is>
+      </c>
+      <c r="H13" s="95" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1" s="83">
+      <c r="A14" s="95" t="inlineStr">
+        <is>
+          <t>GAP-01</t>
+        </is>
+      </c>
+      <c r="B14" s="95" t="inlineStr">
+        <is>
+          <t>2.5·2.6 관련 / 구현 작업 미분해</t>
+        </is>
+      </c>
+      <c r="C14" s="95" t="inlineStr">
+        <is>
+          <t>작품·세계관·캐릭터·회차 관리</t>
+        </is>
+      </c>
+      <c r="D14" s="95" t="inlineStr">
+        <is>
+          <t>기존 요구사항 대비 작업 공백</t>
+        </is>
+      </c>
+      <c r="E14" s="95" t="inlineStr">
+        <is>
+          <t>F-WLD-01~04·08, F-CHR-01~06, F-PUB-01~04, F-SET-01~03. UC-01·02·05·06·13·24. 세계관(UC-02)과 작품(UC-24) 생성 분리.</t>
+        </is>
+      </c>
+      <c r="F14" s="95" t="inlineStr">
+        <is>
+          <t>DB 구축은 CRUD·권한·회차 발행 구현을 대신하지 않음. 현재 WBS 제목에는 별도 업무 패키지가 없음.</t>
+        </is>
+      </c>
+      <c r="G14" s="95" t="inlineStr">
+        <is>
+          <t>실제 산출물 기준으로 구현 작업 분해 필요. 담당·일정은 팀 합의 전 공란 유지.</t>
+        </is>
+      </c>
+      <c r="H14" s="95" t="inlineStr">
         <is>
           <t>usecase v3 반영</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="44" customHeight="1" s="83">
-      <c r="A7" s="67" t="inlineStr">
-        <is>
-          <t>DOC-02</t>
-        </is>
-      </c>
-      <c r="B7" s="67" t="inlineStr">
-        <is>
-          <t>1.5·1.6 / 이번 문서 정리</t>
-        </is>
-      </c>
-      <c r="C7" s="67" t="inlineStr">
-        <is>
-          <t>요구사항·WBS 기준 정합화</t>
-        </is>
-      </c>
-      <c r="D7" s="67" t="inlineStr">
-        <is>
-          <t>이번 반영 / 기능 개발 아님</t>
-        </is>
-      </c>
-      <c r="E7" s="67" t="inlineStr">
-        <is>
-          <t>요구사항 80개 ID 유지, UC·명세·구현·관련 WBS 열 및 정리 기준 추가. WBS 원본 간트 보존.</t>
-        </is>
-      </c>
-      <c r="F7" s="67" t="inlineStr">
-        <is>
-          <t>원본 완료 15개·0% 44개·미입력 1개는 팀 기록이며 이번에 실제 완료를 재검증한 수치가 아님.</t>
-        </is>
-      </c>
-      <c r="G7" s="67" t="inlineStr">
-        <is>
-          <t>향후 완료 보고에는 기능 ID·관련 WBS·검증 근거를 함께 남김.</t>
-        </is>
-      </c>
-      <c r="H7" s="67" t="inlineStr">
+    <row r="15" ht="44" customHeight="1" s="83">
+      <c r="A15" s="95" t="inlineStr">
+        <is>
+          <t>GAP-02</t>
+        </is>
+      </c>
+      <c r="B15" s="95" t="inlineStr">
+        <is>
+          <t>3.1·4.7 관련 / 추출 작업 미분해</t>
+        </is>
+      </c>
+      <c r="C15" s="95" t="inlineStr">
+        <is>
+          <t>원고 등록·설정 추출·확정</t>
+        </is>
+      </c>
+      <c r="D15" s="95" t="inlineStr">
+        <is>
+          <t>기존 요구사항 대비 작업 공백</t>
+        </is>
+      </c>
+      <c r="E15" s="95" t="inlineStr">
+        <is>
+          <t>F-WLD-05~07. UC-03~04. 원고 전처리와 사용자 원고 등록·AI 추출 서비스는 서로 다른 작업.</t>
+        </is>
+      </c>
+      <c r="F15" s="95" t="inlineStr">
+        <is>
+          <t>입력 형식·회차 구분·중복·근거 추출·사용자 채택·저장 계약 미정.</t>
+        </is>
+      </c>
+      <c r="G15" s="95" t="inlineStr">
+        <is>
+          <t>등록 → 후보 추출 → 검토·확정 흐름을 작업 단위로 분해. 자동 공개·학습은 제외.</t>
+        </is>
+      </c>
+      <c r="H15" s="95" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="44" customHeight="1" s="83">
-      <c r="A8" s="67" t="inlineStr">
-        <is>
-          <t>CHECK-01</t>
-        </is>
-      </c>
-      <c r="B8" s="67" t="inlineStr">
-        <is>
-          <t>1.1~1.10·2.1·2.2·7.10·7.2·7.3</t>
-        </is>
-      </c>
-      <c r="C8" s="67" t="inlineStr">
-        <is>
-          <t>기존 완료 표시</t>
-        </is>
-      </c>
-      <c r="D8" s="67" t="inlineStr">
-        <is>
-          <t>기존 기록 보존 / 재검증 안함</t>
-        </is>
-      </c>
-      <c r="E8" s="67" t="inlineStr">
-        <is>
-          <t>원본 갠트 H열 100% 15개. 산출물·회의·수집 완료 여부를 이번에 전부 확인하지 않음.</t>
-        </is>
-      </c>
-      <c r="F8" s="67" t="inlineStr">
-        <is>
-          <t>날짜가 지났거나 완료율이 기록되어 있다는 이유만으로 완료 근거를 만들지 않음.</t>
-        </is>
-      </c>
-      <c r="G8" s="67" t="inlineStr">
-        <is>
-          <t>담당자·산출물 확인이 필요한 시점에 원본 값을 갱신.</t>
-        </is>
-      </c>
-      <c r="H8" s="67" t="inlineStr">
+    <row r="16" ht="44" customHeight="1" s="83">
+      <c r="A16" s="95" t="inlineStr">
+        <is>
+          <t>GAP-03</t>
+        </is>
+      </c>
+      <c r="B16" s="95" t="inlineStr">
+        <is>
+          <t>4.8·5.6 관련 / 집필 작업 미분해</t>
+        </is>
+      </c>
+      <c r="C16" s="95" t="inlineStr">
+        <is>
+          <t>시뮬레이션 화면·집필·버전</t>
+        </is>
+      </c>
+      <c r="D16" s="95" t="inlineStr">
+        <is>
+          <t>기존 요구사항 대비 작업 공백</t>
+        </is>
+      </c>
+      <c r="E16" s="95" t="inlineStr">
+        <is>
+          <t>F-SIM-01~10, F-WRT-01~08·11. UC-09~13.</t>
+        </is>
+      </c>
+      <c r="F16" s="95" t="inlineStr">
+        <is>
+          <t>인물 에이전트 개발은 실행 화면·사용자 선택·집필 편집기·버전 관리 완료와 다름. 5.6 제목은 PR·피드백 화면 중심.</t>
+        </is>
+      </c>
+      <c r="G16" s="95" t="inlineStr">
+        <is>
+          <t>원고 편집·버전·발행과 시뮬레이션 실행/선택 계약을 분리해 일정 검토.</t>
+        </is>
+      </c>
+      <c r="H16" s="95" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1" s="83">
-      <c r="A9" s="67" t="inlineStr">
-        <is>
-          <t>CHECK-02</t>
-        </is>
-      </c>
-      <c r="B9" s="67" t="inlineStr">
-        <is>
-          <t>1.11</t>
-        </is>
-      </c>
-      <c r="C9" s="67" t="inlineStr">
-        <is>
-          <t>3회차 멘토링</t>
-        </is>
-      </c>
-      <c r="D9" s="67" t="inlineStr">
-        <is>
-          <t>완료율 미입력 / 원본 보존</t>
-        </is>
-      </c>
-      <c r="E9" s="67" t="inlineStr">
-        <is>
-          <t>원본 일정 2026-10-29, 완료율 공란.</t>
-        </is>
-      </c>
-      <c r="F9" s="67" t="inlineStr">
-        <is>
-          <t>공란을 0% 또는 완료로 자동 변환하지 않음.</t>
-        </is>
-      </c>
-      <c r="G9" s="67" t="inlineStr">
-        <is>
-          <t>실제 진행 후 담당자가 기록.</t>
-        </is>
-      </c>
-      <c r="H9" s="67" t="inlineStr">
+    <row r="17" ht="44" customHeight="1" s="83">
+      <c r="A17" s="95" t="inlineStr">
+        <is>
+          <t>GAP-04</t>
+        </is>
+      </c>
+      <c r="B17" s="95" t="inlineStr">
+        <is>
+          <t>조건부 / 기존 WBS 명시 없음</t>
+        </is>
+      </c>
+      <c r="C17" s="95" t="inlineStr">
+        <is>
+          <t>AI 크레딧·저장·자율 연재</t>
+        </is>
+      </c>
+      <c r="D17" s="95" t="inlineStr">
+        <is>
+          <t>부담 주체·자동 발행 확정 / 금액·실행 주기 미정</t>
+        </is>
+      </c>
+      <c r="E17" s="95" t="inlineStr">
+        <is>
+          <t>UC-17~19, F-WRT-09~10, F-CRD-01~03, F-STO-01.</t>
+        </is>
+      </c>
+      <c r="F17" s="95" t="inlineStr">
+        <is>
+          <t>가격·무료 제공량·차감 시점·복구, 자율 연재 실행 주기·스케줄러 미정. 인프라·결제 추가를 승인하지 않음.</t>
+        </is>
+      </c>
+      <c r="G17" s="95" t="inlineStr">
+        <is>
+          <t>크레딧·자율 연재 구현 작업과 담당·일정 추가 필요.</t>
+        </is>
+      </c>
+      <c r="H17" s="95" t="inlineStr">
+        <is>
+          <t>usecase v3 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="44" customHeight="1" s="83">
+      <c r="A18" s="95" t="inlineStr">
+        <is>
+          <t>GAP-05</t>
+        </is>
+      </c>
+      <c r="B18" s="95" t="inlineStr">
+        <is>
+          <t>5.6 관련 / 운영 세부 미분해</t>
+        </is>
+      </c>
+      <c r="C18" s="95" t="inlineStr">
+        <is>
+          <t>권리 신고·비공개·소명, 실패·지연 경고</t>
+        </is>
+      </c>
+      <c r="D18" s="95" t="inlineStr">
+        <is>
+          <t>흐름 확정 / 세부 절차 미정</t>
+        </is>
+      </c>
+      <c r="E18" s="95" t="inlineStr">
+        <is>
+          <t>UC-20~21, F-RPT-01·02, F-ALT-01·02.</t>
+        </is>
+      </c>
+      <c r="F18" s="95" t="inlineStr">
+        <is>
+          <t>증빙·소명 기한·허위 신고 대응·경고 채널·로그 보관 미정.</t>
+        </is>
+      </c>
+      <c r="G18" s="95" t="inlineStr">
+        <is>
+          <t>5.6에 운영자 경고·신고 화면 포함, 백엔드 신고·알림 API 작업 추가 필요.</t>
+        </is>
+      </c>
+      <c r="H18" s="95" t="inlineStr">
+        <is>
+          <t>usecase v3 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" s="83">
+      <c r="A19" s="95" t="inlineStr">
+        <is>
+          <t>CHECK-04</t>
+        </is>
+      </c>
+      <c r="B19" s="95" t="inlineStr">
+        <is>
+          <t>6.10·7.10</t>
+        </is>
+      </c>
+      <c r="C19" s="95" t="inlineStr">
+        <is>
+          <t>WBS 식별자 표기 검토</t>
+        </is>
+      </c>
+      <c r="D19" s="95" t="inlineStr">
+        <is>
+          <t>원본 유지 / 확인 필요</t>
+        </is>
+      </c>
+      <c r="E19" s="95" t="inlineStr">
+        <is>
+          <t>6.10 다음이 6.2, 7.10 다음이 7.2로 기록됨.</t>
+        </is>
+      </c>
+      <c r="F19" s="95" t="inlineStr">
+        <is>
+          <t>6.1·7.1의 오기일 수 있으나 확인 없이 식별자를 변경하지 않음.</t>
+        </is>
+      </c>
+      <c r="G19" s="95" t="inlineStr">
+        <is>
+          <t>기존 공유 문서·참조 확인 후 변경 여부 결정.</t>
+        </is>
+      </c>
+      <c r="H19" s="95" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="44" customHeight="1" s="83">
-      <c r="A10" s="67" t="inlineStr">
-        <is>
-          <t>CHECK-03</t>
-        </is>
-      </c>
-      <c r="B10" s="67" t="inlineStr">
-        <is>
-          <t>2.3·2.4·3.1~3.7·4.3~4.5</t>
-        </is>
-      </c>
-      <c r="C10" s="67" t="inlineStr">
-        <is>
-          <t>데이터·학습·검색 작업</t>
-        </is>
-      </c>
-      <c r="D10" s="67" t="inlineStr">
-        <is>
-          <t>기존 0% 보존 / 진행 별도 확인</t>
-        </is>
-      </c>
-      <c r="E10" s="67" t="inlineStr">
-        <is>
-          <t>기획 후보와 원본 일정은 존재. 외부 작업·데이터 수집·학습 결과는 이번 검토 범위에서 확인하지 않음.</t>
-        </is>
-      </c>
-      <c r="F10" s="67" t="inlineStr">
-        <is>
-          <t>저장소 부재만으로 팀의 외부 작업 부재를 단정하지 않음. 데이터 이용 조건·평가 목적 확인 필요.</t>
-        </is>
-      </c>
-      <c r="G10" s="67" t="inlineStr">
-        <is>
-          <t>담당자 산출물 확인 전 진행률 임의 변경 금지. 모델·벡터DB는 기존 계획이며 채택 검증과 구분.</t>
-        </is>
-      </c>
-      <c r="H10" s="67" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="44" customHeight="1" s="83">
-      <c r="A11" s="67" t="inlineStr">
-        <is>
-          <t>DEV-01</t>
-        </is>
-      </c>
-      <c r="B11" s="67" t="inlineStr">
-        <is>
-          <t>2.5·2.6·5.7</t>
-        </is>
-      </c>
-      <c r="C11" s="67" t="inlineStr">
-        <is>
-          <t>데이터 기반·인증</t>
-        </is>
-      </c>
-      <c r="D11" s="67" t="inlineStr">
-        <is>
-          <t>업무 구현 없음 / 계약 미정</t>
-        </is>
-      </c>
-      <c r="E11" s="67" t="inlineStr">
-        <is>
-          <t>../README.md; 현재 Core 소스는 Health만 존재. F-ACT·F-OPS 관련.</t>
-        </is>
-      </c>
-      <c r="F11" s="67" t="inlineStr">
-        <is>
-          <t>DB·인증 방식·권한·계정 수명주기 미정. 현행 저장소에 DB·로그인 없음.</t>
-        </is>
-      </c>
-      <c r="G11" s="67" t="inlineStr">
-        <is>
-          <t>착수 기능의 권한·저장 범위를 합의한 뒤 DB·API·화면 계약 구체화.</t>
-        </is>
-      </c>
-      <c r="H11" s="67" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="44" customHeight="1" s="83">
-      <c r="A12" s="67" t="inlineStr">
-        <is>
-          <t>DEV-02</t>
-        </is>
-      </c>
-      <c r="B12" s="67" t="inlineStr">
-        <is>
-          <t>4.6~4.9·5.9</t>
-        </is>
-      </c>
-      <c r="C12" s="67" t="inlineStr">
-        <is>
-          <t>AI 업무·LLM 연동</t>
-        </is>
-      </c>
-      <c r="D12" s="67" t="inlineStr">
-        <is>
-          <t>미구현</t>
-        </is>
-      </c>
-      <c r="E12" s="67" t="inlineStr">
-        <is>
-          <t>../backend/ai-service/app/main.py; health/router.py. 실행 Agent·모델 호출 없음.</t>
-        </is>
-      </c>
-      <c r="F12" s="67" t="inlineStr">
-        <is>
-          <t>OpenAI Agents SDK 의존성이나 Health 연결은 생성 기능 완료 증거가 아님.</t>
-        </is>
-      </c>
-      <c r="G12" s="67" t="inlineStr">
-        <is>
-          <t>AI 입력·출력·허용 문맥과 실패 처리 계약을 정한 기능부터 구현.</t>
-        </is>
-      </c>
-      <c r="H12" s="67" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="44" customHeight="1" s="83">
-      <c r="A13" s="67" t="inlineStr">
-        <is>
-          <t>DEV-03</t>
-        </is>
-      </c>
-      <c r="B13" s="67" t="inlineStr">
-        <is>
-          <t>5.4~5.8</t>
-        </is>
-      </c>
-      <c r="C13" s="67" t="inlineStr">
-        <is>
-          <t>서비스 화면·업무 API</t>
-        </is>
-      </c>
-      <c r="D13" s="67" t="inlineStr">
-        <is>
-          <t>미구현 / 시작 화면만 존재</t>
-        </is>
-      </c>
-      <c r="E13" s="67" t="inlineStr">
-        <is>
-          <t>../frontend/src/App.tsx; Core Health Controller 2개. 요구사항 80개 전부 미구현.</t>
-        </is>
-      </c>
-      <c r="F13" s="67" t="inlineStr">
-        <is>
-          <t>시작 화면을 공통 업무 레이아웃·독자/작가 화면·인증/Fork API 완료로 계산하지 않음.</t>
-        </is>
-      </c>
-      <c r="G13" s="67" t="inlineStr">
-        <is>
-          <t>선택 기능 단위로 관련 요구사항과 화면·API·수용 기준 연결.</t>
-        </is>
-      </c>
-      <c r="H13" s="67" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="44" customHeight="1" s="83">
-      <c r="A14" s="67" t="inlineStr">
-        <is>
-          <t>GAP-01</t>
-        </is>
-      </c>
-      <c r="B14" s="67" t="inlineStr">
-        <is>
-          <t>2.5·2.6 관련 / 구현 작업 미분해</t>
-        </is>
-      </c>
-      <c r="C14" s="67" t="inlineStr">
-        <is>
-          <t>작품·세계관·캐릭터·회차 관리</t>
-        </is>
-      </c>
-      <c r="D14" s="67" t="inlineStr">
-        <is>
-          <t>기존 요구사항 대비 작업 공백</t>
-        </is>
-      </c>
-      <c r="E14" s="67" t="inlineStr">
-        <is>
-          <t>F-WLD-01~04·08, F-CHR-01~06, F-PUB-01~04, F-SET-01~03. UC-01·02·05·06·13·24. 세계관(UC-02)과 작품(UC-24) 생성 분리.</t>
-        </is>
-      </c>
-      <c r="F14" s="67" t="inlineStr">
-        <is>
-          <t>DB 구축은 CRUD·권한·회차 발행 구현을 대신하지 않음. 현재 WBS 제목에는 별도 업무 패키지가 없음.</t>
-        </is>
-      </c>
-      <c r="G14" s="67" t="inlineStr">
-        <is>
-          <t>실제 산출물 기준으로 구현 작업 분해 필요. 담당·일정은 팀 합의 전 공란 유지.</t>
-        </is>
-      </c>
-      <c r="H14" s="67" t="inlineStr">
-        <is>
-          <t>usecase v3 반영</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="44" customHeight="1" s="83">
-      <c r="A15" s="67" t="inlineStr">
-        <is>
-          <t>GAP-02</t>
-        </is>
-      </c>
-      <c r="B15" s="67" t="inlineStr">
-        <is>
-          <t>3.1·4.7 관련 / 추출 작업 미분해</t>
-        </is>
-      </c>
-      <c r="C15" s="67" t="inlineStr">
-        <is>
-          <t>원고 등록·설정 추출·확정</t>
-        </is>
-      </c>
-      <c r="D15" s="67" t="inlineStr">
-        <is>
-          <t>기존 요구사항 대비 작업 공백</t>
-        </is>
-      </c>
-      <c r="E15" s="67" t="inlineStr">
-        <is>
-          <t>F-WLD-05~07. UC-03~04. 원고 전처리와 사용자 원고 등록·AI 추출 서비스는 서로 다른 작업.</t>
-        </is>
-      </c>
-      <c r="F15" s="67" t="inlineStr">
-        <is>
-          <t>입력 형식·회차 구분·중복·근거 추출·사용자 채택·저장 계약 미정.</t>
-        </is>
-      </c>
-      <c r="G15" s="67" t="inlineStr">
-        <is>
-          <t>등록 → 후보 추출 → 검토·확정 흐름을 작업 단위로 분해. 자동 공개·학습은 제외.</t>
-        </is>
-      </c>
-      <c r="H15" s="67" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="44" customHeight="1" s="83">
-      <c r="A16" s="67" t="inlineStr">
-        <is>
-          <t>GAP-03</t>
-        </is>
-      </c>
-      <c r="B16" s="67" t="inlineStr">
-        <is>
-          <t>4.8·5.6 관련 / 집필 작업 미분해</t>
-        </is>
-      </c>
-      <c r="C16" s="67" t="inlineStr">
-        <is>
-          <t>시뮬레이션 화면·집필·버전</t>
-        </is>
-      </c>
-      <c r="D16" s="67" t="inlineStr">
-        <is>
-          <t>기존 요구사항 대비 작업 공백</t>
-        </is>
-      </c>
-      <c r="E16" s="67" t="inlineStr">
-        <is>
-          <t>F-SIM-01~10, F-WRT-01~08·11. UC-09~13.</t>
-        </is>
-      </c>
-      <c r="F16" s="67" t="inlineStr">
-        <is>
-          <t>인물 에이전트 개발은 실행 화면·사용자 선택·집필 편집기·버전 관리 완료와 다름. 5.6 제목은 PR·피드백 화면 중심.</t>
-        </is>
-      </c>
-      <c r="G16" s="67" t="inlineStr">
-        <is>
-          <t>원고 편집·버전·발행과 시뮬레이션 실행/선택 계약을 분리해 일정 검토.</t>
-        </is>
-      </c>
-      <c r="H16" s="67" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="44" customHeight="1" s="83">
-      <c r="A17" s="67" t="inlineStr">
-        <is>
-          <t>GAP-04</t>
-        </is>
-      </c>
-      <c r="B17" s="67" t="inlineStr">
-        <is>
-          <t>조건부 / 기존 WBS 명시 없음</t>
-        </is>
-      </c>
-      <c r="C17" s="67" t="inlineStr">
-        <is>
-          <t>AI 크레딧·저장·자율 연재</t>
-        </is>
-      </c>
-      <c r="D17" s="67" t="inlineStr">
-        <is>
-          <t>부담 주체·자동 발행 확정 / 금액·실행 주기 미정</t>
-        </is>
-      </c>
-      <c r="E17" s="67" t="inlineStr">
-        <is>
-          <t>UC-17~19, F-WRT-09~10, F-CRD-01~03, F-STO-01.</t>
-        </is>
-      </c>
-      <c r="F17" s="67" t="inlineStr">
-        <is>
-          <t>가격·무료 제공량·차감 시점·복구, 자율 연재 실행 주기·스케줄러 미정. 인프라·결제 추가를 승인하지 않음.</t>
-        </is>
-      </c>
-      <c r="G17" s="67" t="inlineStr">
-        <is>
-          <t>크레딧·자율 연재 구현 작업과 담당·일정 추가 필요.</t>
-        </is>
-      </c>
-      <c r="H17" s="67" t="inlineStr">
-        <is>
-          <t>usecase v3 반영</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="44" customHeight="1" s="83">
-      <c r="A18" s="67" t="inlineStr">
-        <is>
-          <t>GAP-05</t>
-        </is>
-      </c>
-      <c r="B18" s="67" t="inlineStr">
-        <is>
-          <t>5.6 관련 / 운영 세부 미분해</t>
-        </is>
-      </c>
-      <c r="C18" s="67" t="inlineStr">
-        <is>
-          <t>권리 신고·비공개·소명, 실패·지연 경고</t>
-        </is>
-      </c>
-      <c r="D18" s="67" t="inlineStr">
-        <is>
-          <t>흐름 확정 / 세부 절차 미정</t>
-        </is>
-      </c>
-      <c r="E18" s="67" t="inlineStr">
-        <is>
-          <t>UC-20~21, F-RPT-01·02, F-ALT-01·02.</t>
-        </is>
-      </c>
-      <c r="F18" s="67" t="inlineStr">
-        <is>
-          <t>증빙·소명 기한·허위 신고 대응·경고 채널·로그 보관 미정.</t>
-        </is>
-      </c>
-      <c r="G18" s="67" t="inlineStr">
-        <is>
-          <t>5.6에 운영자 경고·신고 화면 포함, 백엔드 신고·알림 API 작업 추가 필요.</t>
-        </is>
-      </c>
-      <c r="H18" s="67" t="inlineStr">
-        <is>
-          <t>usecase v3 반영</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1" s="83">
-      <c r="A19" s="67" t="inlineStr">
-        <is>
-          <t>CHECK-04</t>
-        </is>
-      </c>
-      <c r="B19" s="67" t="inlineStr">
-        <is>
-          <t>6.10·7.10</t>
-        </is>
-      </c>
-      <c r="C19" s="67" t="inlineStr">
-        <is>
-          <t>WBS 식별자 표기 검토</t>
-        </is>
-      </c>
-      <c r="D19" s="67" t="inlineStr">
-        <is>
-          <t>원본 유지 / 확인 필요</t>
-        </is>
-      </c>
-      <c r="E19" s="67" t="inlineStr">
-        <is>
-          <t>6.10 다음이 6.2, 7.10 다음이 7.2로 기록됨.</t>
-        </is>
-      </c>
-      <c r="F19" s="67" t="inlineStr">
-        <is>
-          <t>6.1·7.1의 오기일 수 있으나 확인 없이 식별자를 변경하지 않음.</t>
-        </is>
-      </c>
-      <c r="G19" s="67" t="inlineStr">
-        <is>
-          <t>기존 공유 문서·참조 확인 후 변경 여부 결정.</t>
-        </is>
-      </c>
-      <c r="H19" s="67" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-    </row>
     <row r="20" ht="44" customHeight="1" s="83">
-      <c r="A20" s="67" t="inlineStr">
+      <c r="A20" s="95" t="inlineStr">
         <is>
           <t>CHECK-05</t>
         </is>
       </c>
-      <c r="B20" s="67" t="inlineStr">
+      <c r="B20" s="95" t="inlineStr">
         <is>
           <t>5.0 및 전체 일정</t>
         </is>
       </c>
-      <c r="C20" s="67" t="inlineStr">
+      <c r="C20" s="95" t="inlineStr">
         <is>
           <t>분류명·일정 보존</t>
         </is>
       </c>
-      <c r="D20" s="67" t="inlineStr">
+      <c r="D20" s="95" t="inlineStr">
         <is>
           <t>원본 기준 유지</t>
         </is>
       </c>
-      <c r="E20" s="67" t="inlineStr">
+      <c r="E20" s="95" t="inlineStr">
         <is>
           <t>5.0은 모델 배포라는 제목 안에 화면·인증·API·통합·테스트를 포함. 원본 문서 날짜는 2026-10-23.</t>
         </is>
       </c>
-      <c r="F20" s="67" t="inlineStr">
+      <c r="F20" s="95" t="inlineStr">
         <is>
           <t>업무 범위보다 제목이 좁음. 본 시트 검토일과 원본 일정 작성일은 다름.</t>
         </is>
       </c>
-      <c r="G20" s="67" t="inlineStr">
+      <c r="G20" s="95" t="inlineStr">
         <is>
           <t>다음 일정 합의 때 서비스 개발·통합·배포 등 분류명 검토. 이번에는 기간·소유자·간트 색상 유지.</t>
         </is>
       </c>
-      <c r="H20" s="67" t="inlineStr">
+      <c r="H20" s="95" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
@@ -9713,12 +9713,12 @@
       </c>
       <c r="E21" s="95" t="inlineStr">
         <is>
-          <t>usecase.md §6.2: 세계관·인물관계도는 Gitea로 변경 이력 관리, 회차 원고는 DB.</t>
+          <t>usecase.md §6.2: 세계관·인물관계도는 Gitea로 변경 이력 관리(HEAD 위 새 버전, 덮어쓰기·머지 없음), 회차 원고는 DB. 작품 Fork는 분기 시점 버전 참조, 세계관 Fork는 출처 기록.</t>
         </is>
       </c>
       <c r="F21" s="95" t="inlineStr">
         <is>
-          <t>새 외부 서비스. 구축·연동·백업 작업과 Core API 연동 범위가 WBS에 없음.</t>
+          <t>새 외부 서비스. 구축·연동·백업, 버전 참조·세계관 Fork 복사·작품별 회차 기록 저장 작업과 Core API 연동 범위가 WBS에 없음.</t>
         </is>
       </c>
       <c r="G21" s="95" t="inlineStr">
@@ -9728,7 +9728,7 @@
       </c>
       <c r="H21" s="95" t="inlineStr">
         <is>
-          <t>usecase v3 반영</t>
+          <t>usecase v5 반영</t>
         </is>
       </c>
     </row>
@@ -9813,6 +9813,48 @@
       <c r="H23" s="95" t="inlineStr">
         <is>
           <t>usecase v3 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="44" customHeight="1" s="83">
+      <c r="A24" s="95" t="inlineStr">
+        <is>
+          <t>DOC-03</t>
+        </is>
+      </c>
+      <c r="B24" s="95" t="inlineStr">
+        <is>
+          <t>5.1·5.2 관련</t>
+        </is>
+      </c>
+      <c r="C24" s="95" t="inlineStr">
+        <is>
+          <t>UI 프로토타입 ↔ 유스케이스 대응</t>
+        </is>
+      </c>
+      <c r="D24" s="95" t="inlineStr">
+        <is>
+          <t>대응표 작성 / 프로토타입 정정 남음</t>
+        </is>
+      </c>
+      <c r="E24" s="95" t="inlineStr">
+        <is>
+          <t>docs/prototype-alignment.md; frontend/index.html 정적 프로토타입</t>
+        </is>
+      </c>
+      <c r="F24" s="95" t="inlineStr">
+        <is>
+          <t>프로토타입은 견본이며 정책 근거가 아님. 정정 항목 P-02~P-14 남음.</t>
+        </is>
+      </c>
+      <c r="G24" s="95" t="inlineStr">
+        <is>
+          <t>프론트 담당이 정정 항목 반영 후 대응표 갱신. 화면설계(5.1·5.2) 참고 자료로 사용.</t>
+        </is>
+      </c>
+      <c r="H24" s="95" t="inlineStr">
+        <is>
+          <t>usecase v5 반영</t>
         </is>
       </c>
     </row>

--- a/docs/SKN34-final-4Team_WBS.xlsx
+++ b/docs/SKN34-final-4Team_WBS.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="갠트 차트 템플릿" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="개발현황" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="갠트 차트 템플릿" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발현황" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'개발현황'!$A$3:$H$20</definedName>
@@ -989,7 +989,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ77"/>
+  <dimension ref="A1:BQ86"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1" outlineLevelRow="1"/>
   <cols>
     <col width="4.25" customWidth="1" style="83" min="1" max="1"/>
@@ -7905,15 +7905,693 @@
       <c r="BP77" s="79" t="n"/>
       <c r="BQ77" s="65" t="n"/>
     </row>
-    <row r="78" ht="15.75" customHeight="1" s="83"/>
-    <row r="79" ht="15.75" customHeight="1" s="83"/>
-    <row r="80" ht="15.75" customHeight="1" s="83"/>
-    <row r="81" ht="15.75" customHeight="1" s="83"/>
-    <row r="82" ht="15.75" customHeight="1" s="83"/>
-    <row r="83" ht="15.75" customHeight="1" s="83"/>
-    <row r="84" ht="15.75" customHeight="1" s="83"/>
-    <row r="85" ht="15.75" customHeight="1" s="83"/>
-    <row r="86" ht="15.75" customHeight="1" s="83"/>
+    <row r="78" ht="17.25" customHeight="1" s="83">
+      <c r="A78" s="53" t="n"/>
+      <c r="B78" s="54" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C78" s="56" t="inlineStr">
+        <is>
+          <t>v6 추가 작업 (담당·일정 미정)</t>
+        </is>
+      </c>
+      <c r="D78" s="56" t="n"/>
+      <c r="E78" s="57" t="n"/>
+      <c r="F78" s="57" t="n"/>
+      <c r="G78" s="58" t="n"/>
+      <c r="H78" s="59" t="n"/>
+      <c r="I78" s="60" t="n"/>
+      <c r="J78" s="61" t="n"/>
+      <c r="K78" s="62" t="n"/>
+      <c r="L78" s="62" t="n"/>
+      <c r="M78" s="62" t="n"/>
+      <c r="N78" s="62" t="n"/>
+      <c r="O78" s="62" t="n"/>
+      <c r="P78" s="62" t="n"/>
+      <c r="Q78" s="62" t="n"/>
+      <c r="R78" s="62" t="n"/>
+      <c r="S78" s="62" t="n"/>
+      <c r="T78" s="62" t="n"/>
+      <c r="U78" s="62" t="n"/>
+      <c r="V78" s="62" t="n"/>
+      <c r="W78" s="62" t="n"/>
+      <c r="X78" s="62" t="n"/>
+      <c r="Y78" s="62" t="n"/>
+      <c r="Z78" s="62" t="n"/>
+      <c r="AA78" s="62" t="n"/>
+      <c r="AB78" s="62" t="n"/>
+      <c r="AC78" s="62" t="n"/>
+      <c r="AD78" s="62" t="n"/>
+      <c r="AE78" s="62" t="n"/>
+      <c r="AF78" s="62" t="n"/>
+      <c r="AG78" s="62" t="n"/>
+      <c r="AH78" s="62" t="n"/>
+      <c r="AI78" s="62" t="n"/>
+      <c r="AJ78" s="62" t="n"/>
+      <c r="AK78" s="62" t="n"/>
+      <c r="AL78" s="62" t="n"/>
+      <c r="AM78" s="62" t="n"/>
+      <c r="AN78" s="62" t="n"/>
+      <c r="AO78" s="62" t="n"/>
+      <c r="AP78" s="62" t="n"/>
+      <c r="AQ78" s="62" t="n"/>
+      <c r="AR78" s="62" t="n"/>
+      <c r="AS78" s="62" t="n"/>
+      <c r="AT78" s="62" t="n"/>
+      <c r="AU78" s="62" t="n"/>
+      <c r="AV78" s="62" t="n"/>
+      <c r="AW78" s="62" t="n"/>
+      <c r="AX78" s="62" t="n"/>
+      <c r="AY78" s="62" t="n"/>
+      <c r="AZ78" s="62" t="n"/>
+      <c r="BA78" s="62" t="n"/>
+      <c r="BB78" s="62" t="n"/>
+      <c r="BC78" s="62" t="n"/>
+      <c r="BD78" s="62" t="n"/>
+      <c r="BE78" s="62" t="n"/>
+      <c r="BF78" s="62" t="n"/>
+      <c r="BG78" s="62" t="n"/>
+      <c r="BH78" s="62" t="n"/>
+      <c r="BI78" s="62" t="n"/>
+      <c r="BJ78" s="62" t="n"/>
+      <c r="BK78" s="62" t="n"/>
+      <c r="BL78" s="62" t="n"/>
+      <c r="BM78" s="62" t="n"/>
+      <c r="BN78" s="62" t="n"/>
+      <c r="BO78" s="62" t="n"/>
+      <c r="BP78" s="63" t="n"/>
+      <c r="BQ78" s="64" t="n"/>
+    </row>
+    <row r="79" ht="17.25" customHeight="1" s="83">
+      <c r="A79" s="65" t="n"/>
+      <c r="B79" s="66" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="C79" s="95" t="inlineStr">
+        <is>
+          <t>Gitea 구축·Core 연동 (세계관 버전·Fork 커밋 고정)</t>
+        </is>
+      </c>
+      <c r="D79" s="95" t="n"/>
+      <c r="E79" s="68" t="n"/>
+      <c r="F79" s="68" t="n"/>
+      <c r="G79" s="69" t="n"/>
+      <c r="H79" s="70" t="n"/>
+      <c r="I79" s="71" t="n"/>
+      <c r="J79" s="72" t="n"/>
+      <c r="K79" s="73" t="n"/>
+      <c r="L79" s="73" t="n"/>
+      <c r="P79" s="75" t="n"/>
+      <c r="Q79" s="75" t="n"/>
+      <c r="R79" s="75" t="n"/>
+      <c r="S79" s="73" t="n"/>
+      <c r="T79" s="73" t="n"/>
+      <c r="U79" s="73" t="n"/>
+      <c r="V79" s="73" t="n"/>
+      <c r="W79" s="73" t="n"/>
+      <c r="X79" s="73" t="n"/>
+      <c r="Y79" s="73" t="n"/>
+      <c r="Z79" s="73" t="n"/>
+      <c r="AA79" s="73" t="n"/>
+      <c r="AB79" s="73" t="n"/>
+      <c r="AC79" s="76" t="n"/>
+      <c r="AD79" s="76" t="n"/>
+      <c r="AE79" s="76" t="n"/>
+      <c r="AF79" s="76" t="n"/>
+      <c r="AG79" s="76" t="n"/>
+      <c r="AH79" s="73" t="n"/>
+      <c r="AI79" s="73" t="n"/>
+      <c r="AJ79" s="73" t="n"/>
+      <c r="AK79" s="73" t="n"/>
+      <c r="AL79" s="73" t="n"/>
+      <c r="AM79" s="73" t="n"/>
+      <c r="AN79" s="73" t="n"/>
+      <c r="AO79" s="73" t="n"/>
+      <c r="AP79" s="73" t="n"/>
+      <c r="AQ79" s="73" t="n"/>
+      <c r="AR79" s="77" t="n"/>
+      <c r="AS79" s="77" t="n"/>
+      <c r="AT79" s="77" t="n"/>
+      <c r="AU79" s="77" t="n"/>
+      <c r="AV79" s="77" t="n"/>
+      <c r="AW79" s="73" t="n"/>
+      <c r="AX79" s="73" t="n"/>
+      <c r="AY79" s="73" t="n"/>
+      <c r="AZ79" s="73" t="n"/>
+      <c r="BA79" s="73" t="n"/>
+      <c r="BB79" s="73" t="n"/>
+      <c r="BC79" s="73" t="n"/>
+      <c r="BD79" s="73" t="n"/>
+      <c r="BE79" s="73" t="n"/>
+      <c r="BF79" s="73" t="n"/>
+      <c r="BG79" s="78" t="n"/>
+      <c r="BH79" s="78" t="n"/>
+      <c r="BI79" s="78" t="n"/>
+      <c r="BJ79" s="78" t="n"/>
+      <c r="BK79" s="78" t="n"/>
+      <c r="BL79" s="73" t="n"/>
+      <c r="BM79" s="73" t="n"/>
+      <c r="BN79" s="73" t="n"/>
+      <c r="BO79" s="73" t="n"/>
+      <c r="BP79" s="79" t="n"/>
+      <c r="BQ79" s="65" t="n"/>
+    </row>
+    <row r="80" ht="17.25" customHeight="1" s="83">
+      <c r="A80" s="65" t="n"/>
+      <c r="B80" s="66" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="C80" s="95" t="inlineStr">
+        <is>
+          <t>Elasticsearch 검색 구축·색인 동기화</t>
+        </is>
+      </c>
+      <c r="D80" s="95" t="n"/>
+      <c r="E80" s="68" t="n"/>
+      <c r="F80" s="68" t="n"/>
+      <c r="G80" s="69" t="n"/>
+      <c r="H80" s="70" t="n"/>
+      <c r="I80" s="71" t="n"/>
+      <c r="J80" s="72" t="n"/>
+      <c r="K80" s="73" t="n"/>
+      <c r="L80" s="73" t="n"/>
+      <c r="P80" s="75" t="n"/>
+      <c r="Q80" s="75" t="n"/>
+      <c r="R80" s="75" t="n"/>
+      <c r="S80" s="73" t="n"/>
+      <c r="T80" s="73" t="n"/>
+      <c r="U80" s="73" t="n"/>
+      <c r="V80" s="73" t="n"/>
+      <c r="W80" s="73" t="n"/>
+      <c r="X80" s="73" t="n"/>
+      <c r="Y80" s="73" t="n"/>
+      <c r="Z80" s="73" t="n"/>
+      <c r="AA80" s="73" t="n"/>
+      <c r="AB80" s="73" t="n"/>
+      <c r="AC80" s="76" t="n"/>
+      <c r="AD80" s="76" t="n"/>
+      <c r="AE80" s="76" t="n"/>
+      <c r="AF80" s="76" t="n"/>
+      <c r="AG80" s="76" t="n"/>
+      <c r="AH80" s="73" t="n"/>
+      <c r="AI80" s="73" t="n"/>
+      <c r="AJ80" s="73" t="n"/>
+      <c r="AK80" s="73" t="n"/>
+      <c r="AL80" s="73" t="n"/>
+      <c r="AM80" s="73" t="n"/>
+      <c r="AN80" s="73" t="n"/>
+      <c r="AO80" s="73" t="n"/>
+      <c r="AP80" s="73" t="n"/>
+      <c r="AQ80" s="73" t="n"/>
+      <c r="AR80" s="77" t="n"/>
+      <c r="AS80" s="77" t="n"/>
+      <c r="AT80" s="77" t="n"/>
+      <c r="AU80" s="77" t="n"/>
+      <c r="AV80" s="77" t="n"/>
+      <c r="AW80" s="73" t="n"/>
+      <c r="AX80" s="73" t="n"/>
+      <c r="AY80" s="73" t="n"/>
+      <c r="AZ80" s="73" t="n"/>
+      <c r="BA80" s="73" t="n"/>
+      <c r="BB80" s="73" t="n"/>
+      <c r="BC80" s="73" t="n"/>
+      <c r="BD80" s="73" t="n"/>
+      <c r="BE80" s="73" t="n"/>
+      <c r="BF80" s="73" t="n"/>
+      <c r="BG80" s="78" t="n"/>
+      <c r="BH80" s="78" t="n"/>
+      <c r="BI80" s="78" t="n"/>
+      <c r="BJ80" s="78" t="n"/>
+      <c r="BK80" s="78" t="n"/>
+      <c r="BL80" s="73" t="n"/>
+      <c r="BM80" s="73" t="n"/>
+      <c r="BN80" s="73" t="n"/>
+      <c r="BO80" s="73" t="n"/>
+      <c r="BP80" s="79" t="n"/>
+      <c r="BQ80" s="65" t="n"/>
+    </row>
+    <row r="81" ht="17.25" customHeight="1" s="83">
+      <c r="A81" s="65" t="n"/>
+      <c r="B81" s="66" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="C81" s="95" t="inlineStr">
+        <is>
+          <t>AI Service LangChain·LangGraph 전환·Langfuse(Docker) 구축</t>
+        </is>
+      </c>
+      <c r="D81" s="95" t="n"/>
+      <c r="E81" s="68" t="n"/>
+      <c r="F81" s="68" t="n"/>
+      <c r="G81" s="69" t="n"/>
+      <c r="H81" s="70" t="n"/>
+      <c r="I81" s="71" t="n"/>
+      <c r="J81" s="72" t="n"/>
+      <c r="K81" s="73" t="n"/>
+      <c r="L81" s="73" t="n"/>
+      <c r="P81" s="75" t="n"/>
+      <c r="Q81" s="75" t="n"/>
+      <c r="R81" s="75" t="n"/>
+      <c r="S81" s="73" t="n"/>
+      <c r="T81" s="73" t="n"/>
+      <c r="U81" s="73" t="n"/>
+      <c r="V81" s="73" t="n"/>
+      <c r="W81" s="73" t="n"/>
+      <c r="X81" s="73" t="n"/>
+      <c r="Y81" s="73" t="n"/>
+      <c r="Z81" s="73" t="n"/>
+      <c r="AA81" s="73" t="n"/>
+      <c r="AB81" s="73" t="n"/>
+      <c r="AC81" s="76" t="n"/>
+      <c r="AD81" s="76" t="n"/>
+      <c r="AE81" s="76" t="n"/>
+      <c r="AF81" s="76" t="n"/>
+      <c r="AG81" s="76" t="n"/>
+      <c r="AH81" s="73" t="n"/>
+      <c r="AI81" s="73" t="n"/>
+      <c r="AJ81" s="73" t="n"/>
+      <c r="AK81" s="73" t="n"/>
+      <c r="AL81" s="73" t="n"/>
+      <c r="AM81" s="73" t="n"/>
+      <c r="AN81" s="73" t="n"/>
+      <c r="AO81" s="73" t="n"/>
+      <c r="AP81" s="73" t="n"/>
+      <c r="AQ81" s="73" t="n"/>
+      <c r="AR81" s="77" t="n"/>
+      <c r="AS81" s="77" t="n"/>
+      <c r="AT81" s="77" t="n"/>
+      <c r="AU81" s="77" t="n"/>
+      <c r="AV81" s="77" t="n"/>
+      <c r="AW81" s="73" t="n"/>
+      <c r="AX81" s="73" t="n"/>
+      <c r="AY81" s="73" t="n"/>
+      <c r="AZ81" s="73" t="n"/>
+      <c r="BA81" s="73" t="n"/>
+      <c r="BB81" s="73" t="n"/>
+      <c r="BC81" s="73" t="n"/>
+      <c r="BD81" s="73" t="n"/>
+      <c r="BE81" s="73" t="n"/>
+      <c r="BF81" s="73" t="n"/>
+      <c r="BG81" s="78" t="n"/>
+      <c r="BH81" s="78" t="n"/>
+      <c r="BI81" s="78" t="n"/>
+      <c r="BJ81" s="78" t="n"/>
+      <c r="BK81" s="78" t="n"/>
+      <c r="BL81" s="73" t="n"/>
+      <c r="BM81" s="73" t="n"/>
+      <c r="BN81" s="73" t="n"/>
+      <c r="BO81" s="73" t="n"/>
+      <c r="BP81" s="79" t="n"/>
+      <c r="BQ81" s="65" t="n"/>
+    </row>
+    <row r="82" ht="17.25" customHeight="1" s="83">
+      <c r="A82" s="65" t="n"/>
+      <c r="B82" s="66" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="C82" s="95" t="inlineStr">
+        <is>
+          <t>Core 내장 스케줄러·정기 작업·알림함</t>
+        </is>
+      </c>
+      <c r="D82" s="95" t="n"/>
+      <c r="E82" s="68" t="n"/>
+      <c r="F82" s="68" t="n"/>
+      <c r="G82" s="69" t="n"/>
+      <c r="H82" s="70" t="n"/>
+      <c r="I82" s="71" t="n"/>
+      <c r="J82" s="72" t="n"/>
+      <c r="K82" s="73" t="n"/>
+      <c r="L82" s="73" t="n"/>
+      <c r="P82" s="75" t="n"/>
+      <c r="Q82" s="75" t="n"/>
+      <c r="R82" s="75" t="n"/>
+      <c r="S82" s="73" t="n"/>
+      <c r="T82" s="73" t="n"/>
+      <c r="U82" s="73" t="n"/>
+      <c r="V82" s="73" t="n"/>
+      <c r="W82" s="73" t="n"/>
+      <c r="X82" s="73" t="n"/>
+      <c r="Y82" s="73" t="n"/>
+      <c r="Z82" s="73" t="n"/>
+      <c r="AA82" s="73" t="n"/>
+      <c r="AB82" s="73" t="n"/>
+      <c r="AC82" s="76" t="n"/>
+      <c r="AD82" s="76" t="n"/>
+      <c r="AE82" s="76" t="n"/>
+      <c r="AF82" s="76" t="n"/>
+      <c r="AG82" s="76" t="n"/>
+      <c r="AH82" s="73" t="n"/>
+      <c r="AI82" s="73" t="n"/>
+      <c r="AJ82" s="73" t="n"/>
+      <c r="AK82" s="73" t="n"/>
+      <c r="AL82" s="73" t="n"/>
+      <c r="AM82" s="73" t="n"/>
+      <c r="AN82" s="73" t="n"/>
+      <c r="AO82" s="73" t="n"/>
+      <c r="AP82" s="73" t="n"/>
+      <c r="AQ82" s="73" t="n"/>
+      <c r="AR82" s="77" t="n"/>
+      <c r="AS82" s="77" t="n"/>
+      <c r="AT82" s="77" t="n"/>
+      <c r="AU82" s="77" t="n"/>
+      <c r="AV82" s="77" t="n"/>
+      <c r="AW82" s="73" t="n"/>
+      <c r="AX82" s="73" t="n"/>
+      <c r="AY82" s="73" t="n"/>
+      <c r="AZ82" s="73" t="n"/>
+      <c r="BA82" s="73" t="n"/>
+      <c r="BB82" s="73" t="n"/>
+      <c r="BC82" s="73" t="n"/>
+      <c r="BD82" s="73" t="n"/>
+      <c r="BE82" s="73" t="n"/>
+      <c r="BF82" s="73" t="n"/>
+      <c r="BG82" s="78" t="n"/>
+      <c r="BH82" s="78" t="n"/>
+      <c r="BI82" s="78" t="n"/>
+      <c r="BJ82" s="78" t="n"/>
+      <c r="BK82" s="78" t="n"/>
+      <c r="BL82" s="73" t="n"/>
+      <c r="BM82" s="73" t="n"/>
+      <c r="BN82" s="73" t="n"/>
+      <c r="BO82" s="73" t="n"/>
+      <c r="BP82" s="79" t="n"/>
+      <c r="BQ82" s="65" t="n"/>
+    </row>
+    <row r="83" ht="17.25" customHeight="1" s="83">
+      <c r="A83" s="65" t="n"/>
+      <c r="B83" s="66" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="C83" s="95" t="inlineStr">
+        <is>
+          <t>이미지 저장소·EPUB 가져오기/내보내기·일러스트 생성</t>
+        </is>
+      </c>
+      <c r="D83" s="95" t="n"/>
+      <c r="E83" s="68" t="n"/>
+      <c r="F83" s="68" t="n"/>
+      <c r="G83" s="69" t="n"/>
+      <c r="H83" s="70" t="n"/>
+      <c r="I83" s="71" t="n"/>
+      <c r="J83" s="72" t="n"/>
+      <c r="K83" s="73" t="n"/>
+      <c r="L83" s="73" t="n"/>
+      <c r="P83" s="75" t="n"/>
+      <c r="Q83" s="75" t="n"/>
+      <c r="R83" s="75" t="n"/>
+      <c r="S83" s="73" t="n"/>
+      <c r="T83" s="73" t="n"/>
+      <c r="U83" s="73" t="n"/>
+      <c r="V83" s="73" t="n"/>
+      <c r="W83" s="73" t="n"/>
+      <c r="X83" s="73" t="n"/>
+      <c r="Y83" s="73" t="n"/>
+      <c r="Z83" s="73" t="n"/>
+      <c r="AA83" s="73" t="n"/>
+      <c r="AB83" s="73" t="n"/>
+      <c r="AC83" s="76" t="n"/>
+      <c r="AD83" s="76" t="n"/>
+      <c r="AE83" s="76" t="n"/>
+      <c r="AF83" s="76" t="n"/>
+      <c r="AG83" s="76" t="n"/>
+      <c r="AH83" s="73" t="n"/>
+      <c r="AI83" s="73" t="n"/>
+      <c r="AJ83" s="73" t="n"/>
+      <c r="AK83" s="73" t="n"/>
+      <c r="AL83" s="73" t="n"/>
+      <c r="AM83" s="73" t="n"/>
+      <c r="AN83" s="73" t="n"/>
+      <c r="AO83" s="73" t="n"/>
+      <c r="AP83" s="73" t="n"/>
+      <c r="AQ83" s="73" t="n"/>
+      <c r="AR83" s="77" t="n"/>
+      <c r="AS83" s="77" t="n"/>
+      <c r="AT83" s="77" t="n"/>
+      <c r="AU83" s="77" t="n"/>
+      <c r="AV83" s="77" t="n"/>
+      <c r="AW83" s="73" t="n"/>
+      <c r="AX83" s="73" t="n"/>
+      <c r="AY83" s="73" t="n"/>
+      <c r="AZ83" s="73" t="n"/>
+      <c r="BA83" s="73" t="n"/>
+      <c r="BB83" s="73" t="n"/>
+      <c r="BC83" s="73" t="n"/>
+      <c r="BD83" s="73" t="n"/>
+      <c r="BE83" s="73" t="n"/>
+      <c r="BF83" s="73" t="n"/>
+      <c r="BG83" s="78" t="n"/>
+      <c r="BH83" s="78" t="n"/>
+      <c r="BI83" s="78" t="n"/>
+      <c r="BJ83" s="78" t="n"/>
+      <c r="BK83" s="78" t="n"/>
+      <c r="BL83" s="73" t="n"/>
+      <c r="BM83" s="73" t="n"/>
+      <c r="BN83" s="73" t="n"/>
+      <c r="BO83" s="73" t="n"/>
+      <c r="BP83" s="79" t="n"/>
+      <c r="BQ83" s="65" t="n"/>
+    </row>
+    <row r="84" ht="17.25" customHeight="1" s="83">
+      <c r="A84" s="65" t="n"/>
+      <c r="B84" s="66" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="C84" s="95" t="inlineStr">
+        <is>
+          <t>유해 콘텐츠 필터·스토리 오류 검증 시뮬레이션·반영 보상</t>
+        </is>
+      </c>
+      <c r="D84" s="95" t="n"/>
+      <c r="E84" s="68" t="n"/>
+      <c r="F84" s="68" t="n"/>
+      <c r="G84" s="69" t="n"/>
+      <c r="H84" s="70" t="n"/>
+      <c r="I84" s="71" t="n"/>
+      <c r="J84" s="72" t="n"/>
+      <c r="K84" s="73" t="n"/>
+      <c r="L84" s="73" t="n"/>
+      <c r="P84" s="75" t="n"/>
+      <c r="Q84" s="75" t="n"/>
+      <c r="R84" s="75" t="n"/>
+      <c r="S84" s="73" t="n"/>
+      <c r="T84" s="73" t="n"/>
+      <c r="U84" s="73" t="n"/>
+      <c r="V84" s="73" t="n"/>
+      <c r="W84" s="73" t="n"/>
+      <c r="X84" s="73" t="n"/>
+      <c r="Y84" s="73" t="n"/>
+      <c r="Z84" s="73" t="n"/>
+      <c r="AA84" s="73" t="n"/>
+      <c r="AB84" s="73" t="n"/>
+      <c r="AC84" s="76" t="n"/>
+      <c r="AD84" s="76" t="n"/>
+      <c r="AE84" s="76" t="n"/>
+      <c r="AF84" s="76" t="n"/>
+      <c r="AG84" s="76" t="n"/>
+      <c r="AH84" s="73" t="n"/>
+      <c r="AI84" s="73" t="n"/>
+      <c r="AJ84" s="73" t="n"/>
+      <c r="AK84" s="73" t="n"/>
+      <c r="AL84" s="73" t="n"/>
+      <c r="AM84" s="73" t="n"/>
+      <c r="AN84" s="73" t="n"/>
+      <c r="AO84" s="73" t="n"/>
+      <c r="AP84" s="73" t="n"/>
+      <c r="AQ84" s="73" t="n"/>
+      <c r="AR84" s="77" t="n"/>
+      <c r="AS84" s="77" t="n"/>
+      <c r="AT84" s="77" t="n"/>
+      <c r="AU84" s="77" t="n"/>
+      <c r="AV84" s="77" t="n"/>
+      <c r="AW84" s="73" t="n"/>
+      <c r="AX84" s="73" t="n"/>
+      <c r="AY84" s="73" t="n"/>
+      <c r="AZ84" s="73" t="n"/>
+      <c r="BA84" s="73" t="n"/>
+      <c r="BB84" s="73" t="n"/>
+      <c r="BC84" s="73" t="n"/>
+      <c r="BD84" s="73" t="n"/>
+      <c r="BE84" s="73" t="n"/>
+      <c r="BF84" s="73" t="n"/>
+      <c r="BG84" s="78" t="n"/>
+      <c r="BH84" s="78" t="n"/>
+      <c r="BI84" s="78" t="n"/>
+      <c r="BJ84" s="78" t="n"/>
+      <c r="BK84" s="78" t="n"/>
+      <c r="BL84" s="73" t="n"/>
+      <c r="BM84" s="73" t="n"/>
+      <c r="BN84" s="73" t="n"/>
+      <c r="BO84" s="73" t="n"/>
+      <c r="BP84" s="79" t="n"/>
+      <c r="BQ84" s="65" t="n"/>
+    </row>
+    <row r="85" ht="17.25" customHeight="1" s="83">
+      <c r="A85" s="65" t="n"/>
+      <c r="B85" s="66" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="C85" s="95" t="inlineStr">
+        <is>
+          <t>크레딧 구조(구독·후차감)·요청 속도 제한</t>
+        </is>
+      </c>
+      <c r="D85" s="95" t="n"/>
+      <c r="E85" s="68" t="n"/>
+      <c r="F85" s="68" t="n"/>
+      <c r="G85" s="69" t="n"/>
+      <c r="H85" s="70" t="n"/>
+      <c r="I85" s="71" t="n"/>
+      <c r="J85" s="72" t="n"/>
+      <c r="K85" s="73" t="n"/>
+      <c r="L85" s="73" t="n"/>
+      <c r="P85" s="75" t="n"/>
+      <c r="Q85" s="75" t="n"/>
+      <c r="R85" s="75" t="n"/>
+      <c r="S85" s="73" t="n"/>
+      <c r="T85" s="73" t="n"/>
+      <c r="U85" s="73" t="n"/>
+      <c r="V85" s="73" t="n"/>
+      <c r="W85" s="73" t="n"/>
+      <c r="X85" s="73" t="n"/>
+      <c r="Y85" s="73" t="n"/>
+      <c r="Z85" s="73" t="n"/>
+      <c r="AA85" s="73" t="n"/>
+      <c r="AB85" s="73" t="n"/>
+      <c r="AC85" s="76" t="n"/>
+      <c r="AD85" s="76" t="n"/>
+      <c r="AE85" s="76" t="n"/>
+      <c r="AF85" s="76" t="n"/>
+      <c r="AG85" s="76" t="n"/>
+      <c r="AH85" s="73" t="n"/>
+      <c r="AI85" s="73" t="n"/>
+      <c r="AJ85" s="73" t="n"/>
+      <c r="AK85" s="73" t="n"/>
+      <c r="AL85" s="73" t="n"/>
+      <c r="AM85" s="73" t="n"/>
+      <c r="AN85" s="73" t="n"/>
+      <c r="AO85" s="73" t="n"/>
+      <c r="AP85" s="73" t="n"/>
+      <c r="AQ85" s="73" t="n"/>
+      <c r="AR85" s="77" t="n"/>
+      <c r="AS85" s="77" t="n"/>
+      <c r="AT85" s="77" t="n"/>
+      <c r="AU85" s="77" t="n"/>
+      <c r="AV85" s="77" t="n"/>
+      <c r="AW85" s="73" t="n"/>
+      <c r="AX85" s="73" t="n"/>
+      <c r="AY85" s="73" t="n"/>
+      <c r="AZ85" s="73" t="n"/>
+      <c r="BA85" s="73" t="n"/>
+      <c r="BB85" s="73" t="n"/>
+      <c r="BC85" s="73" t="n"/>
+      <c r="BD85" s="73" t="n"/>
+      <c r="BE85" s="73" t="n"/>
+      <c r="BF85" s="73" t="n"/>
+      <c r="BG85" s="78" t="n"/>
+      <c r="BH85" s="78" t="n"/>
+      <c r="BI85" s="78" t="n"/>
+      <c r="BJ85" s="78" t="n"/>
+      <c r="BK85" s="78" t="n"/>
+      <c r="BL85" s="73" t="n"/>
+      <c r="BM85" s="73" t="n"/>
+      <c r="BN85" s="73" t="n"/>
+      <c r="BO85" s="73" t="n"/>
+      <c r="BP85" s="79" t="n"/>
+      <c r="BQ85" s="65" t="n"/>
+    </row>
+    <row r="86" ht="17.25" customHeight="1" s="83">
+      <c r="A86" s="65" t="n"/>
+      <c r="B86" s="66" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="C86" s="95" t="inlineStr">
+        <is>
+          <t>LLMOps 평가 세트·AI 운영 화면</t>
+        </is>
+      </c>
+      <c r="D86" s="95" t="n"/>
+      <c r="E86" s="68" t="n"/>
+      <c r="F86" s="68" t="n"/>
+      <c r="G86" s="69" t="n"/>
+      <c r="H86" s="70" t="n"/>
+      <c r="I86" s="71" t="n"/>
+      <c r="J86" s="72" t="n"/>
+      <c r="K86" s="73" t="n"/>
+      <c r="L86" s="73" t="n"/>
+      <c r="P86" s="75" t="n"/>
+      <c r="Q86" s="75" t="n"/>
+      <c r="R86" s="75" t="n"/>
+      <c r="S86" s="73" t="n"/>
+      <c r="T86" s="73" t="n"/>
+      <c r="U86" s="73" t="n"/>
+      <c r="V86" s="73" t="n"/>
+      <c r="W86" s="73" t="n"/>
+      <c r="X86" s="73" t="n"/>
+      <c r="Y86" s="73" t="n"/>
+      <c r="Z86" s="73" t="n"/>
+      <c r="AA86" s="73" t="n"/>
+      <c r="AB86" s="73" t="n"/>
+      <c r="AC86" s="76" t="n"/>
+      <c r="AD86" s="76" t="n"/>
+      <c r="AE86" s="76" t="n"/>
+      <c r="AF86" s="76" t="n"/>
+      <c r="AG86" s="76" t="n"/>
+      <c r="AH86" s="73" t="n"/>
+      <c r="AI86" s="73" t="n"/>
+      <c r="AJ86" s="73" t="n"/>
+      <c r="AK86" s="73" t="n"/>
+      <c r="AL86" s="73" t="n"/>
+      <c r="AM86" s="73" t="n"/>
+      <c r="AN86" s="73" t="n"/>
+      <c r="AO86" s="73" t="n"/>
+      <c r="AP86" s="73" t="n"/>
+      <c r="AQ86" s="73" t="n"/>
+      <c r="AR86" s="77" t="n"/>
+      <c r="AS86" s="77" t="n"/>
+      <c r="AT86" s="77" t="n"/>
+      <c r="AU86" s="77" t="n"/>
+      <c r="AV86" s="77" t="n"/>
+      <c r="AW86" s="73" t="n"/>
+      <c r="AX86" s="73" t="n"/>
+      <c r="AY86" s="73" t="n"/>
+      <c r="AZ86" s="73" t="n"/>
+      <c r="BA86" s="73" t="n"/>
+      <c r="BB86" s="73" t="n"/>
+      <c r="BC86" s="73" t="n"/>
+      <c r="BD86" s="73" t="n"/>
+      <c r="BE86" s="73" t="n"/>
+      <c r="BF86" s="73" t="n"/>
+      <c r="BG86" s="78" t="n"/>
+      <c r="BH86" s="78" t="n"/>
+      <c r="BI86" s="78" t="n"/>
+      <c r="BJ86" s="78" t="n"/>
+      <c r="BK86" s="78" t="n"/>
+      <c r="BL86" s="73" t="n"/>
+      <c r="BM86" s="73" t="n"/>
+      <c r="BN86" s="73" t="n"/>
+      <c r="BO86" s="73" t="n"/>
+      <c r="BP86" s="79" t="n"/>
+      <c r="BQ86" s="65" t="n"/>
+    </row>
     <row r="87" ht="15.75" customHeight="1" s="83"/>
     <row r="88" ht="15.75" customHeight="1" s="83"/>
     <row r="89" ht="15.75" customHeight="1" s="83"/>
@@ -8893,7 +9571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="24"/>
   <cols>
     <col width="17" customWidth="1" style="83" min="1" max="1"/>
@@ -8923,7 +9601,7 @@
     <row r="2" ht="42" customHeight="1" s="83">
       <c r="A2" s="95" t="inlineStr">
         <is>
-          <t>2026-10-27 저장소 확인 기준. 원본 간트의 담당자·일정·기간·완료율은 그대로 보존했습니다. 아래 현황은 실행 재검증이나 팀 외부 작업 확인을 대신하지 않습니다.</t>
+          <t>2026-10-27 저장소 확인 기준, 2026-10-28 유스케이스 v6 결정 반영. 원본 간트의 담당자·일정·기간·완료율은 그대로 보존했습니다. 아래 현황은 실행 재검증이나 팀 외부 작업 확인을 대신하지 않습니다.</t>
         </is>
       </c>
       <c r="B2" s="94" t="n"/>
@@ -9078,12 +9756,12 @@
       </c>
       <c r="D6" s="95" t="inlineStr">
         <is>
-          <t>v5 작성 / 일부 정책 미확정</t>
+          <t>v6 작성 / 일부 정책 미확정</t>
         </is>
       </c>
       <c r="E6" s="95" t="inlineStr">
         <is>
-          <t>docs/usecase.md v5, docs/usecase-spec/UC-01~25.md. 세계관·작품 분리, 세계관 버전·세계관 Fork, 자율 연재 자동 발행, 크레딧 부담 주체 등 팀 결정 반영.</t>
+          <t>docs/usecase.md v6, docs/usecase-spec/UC-01~28.md. Fork·원고 입력(EPUB·이미지·일러스트)·계정·피드백(BR-15)·크레딧(후차감·구독)·자율 연재·권리 신고·탐색 정책 확정, UC-26~28 추가, UC-25 채택(MVP 제외).</t>
         </is>
       </c>
       <c r="F6" s="95" t="inlineStr">
@@ -9098,7 +9776,7 @@
       </c>
       <c r="H6" s="95" t="inlineStr">
         <is>
-          <t>usecase v5 반영</t>
+          <t>usecase v6 반영</t>
         </is>
       </c>
     </row>
@@ -9340,7 +10018,7 @@
       </c>
       <c r="F12" s="95" t="inlineStr">
         <is>
-          <t>OpenAI Agents SDK 의존성이나 Health 연결은 생성 기능 완료 증거가 아님.</t>
+          <t>AI 스택은 LangChain·LangGraph·Langfuse로 확정(v6). 남아 있는 openai-agents 의존성이나 Health 연결은 생성 기능 완료 증거가 아님.</t>
         </is>
       </c>
       <c r="G12" s="95" t="inlineStr">
@@ -9540,7 +10218,7 @@
       </c>
       <c r="D17" s="95" t="inlineStr">
         <is>
-          <t>부담 주체·자동 발행 확정 / 금액·실행 주기 미정</t>
+          <t>부담 주체·후차감·자율 연재 일정 확정 / 금액 미정</t>
         </is>
       </c>
       <c r="E17" s="95" t="inlineStr">
@@ -9550,7 +10228,7 @@
       </c>
       <c r="F17" s="95" t="inlineStr">
         <is>
-          <t>가격·무료 제공량·차감 시점·복구, 자율 연재 실행 주기·스케줄러 미정. 인프라·결제 추가를 승인하지 않음.</t>
+          <t>가격·플랜·토큰 환산 비율 미정. 자율 연재는 Core 내장 스케줄러로 확정했지만 구현 작업이 없음. 결제 연동은 승인하지 않음.</t>
         </is>
       </c>
       <c r="G17" s="95" t="inlineStr">
@@ -9560,7 +10238,7 @@
       </c>
       <c r="H17" s="95" t="inlineStr">
         <is>
-          <t>usecase v3 반영</t>
+          <t>usecase v6 반영</t>
         </is>
       </c>
     </row>
@@ -9582,7 +10260,7 @@
       </c>
       <c r="D18" s="95" t="inlineStr">
         <is>
-          <t>흐름 확정 / 세부 절차 미정</t>
+          <t>흐름·기한 확정 / 증빙 기준 미정</t>
         </is>
       </c>
       <c r="E18" s="95" t="inlineStr">
@@ -9592,7 +10270,7 @@
       </c>
       <c r="F18" s="95" t="inlineStr">
         <is>
-          <t>증빙·소명 기한·허위 신고 대응·경고 채널·로그 보관 미정.</t>
+          <t>소명 7일·허위 신고 제한·24시간 1차 조치·경고 채널·로그 90일은 v6 확정. 증빙 기준은 다른 플랫폼 사례 조사 후 반영, 면책 범위는 법률 검토.</t>
         </is>
       </c>
       <c r="G18" s="95" t="inlineStr">
@@ -9602,7 +10280,7 @@
       </c>
       <c r="H18" s="95" t="inlineStr">
         <is>
-          <t>usecase v3 반영</t>
+          <t>usecase v6 반영</t>
         </is>
       </c>
     </row>
@@ -9723,12 +10401,12 @@
       </c>
       <c r="G21" s="95" t="inlineStr">
         <is>
-          <t>Gitea 구축·연동 작업 추가와 담당·일정 합의 필요.</t>
+          <t>Gitea 구축·연동 작업을 간트 8.1로 추가(담당·일정 미정). 담당·일정 합의 필요.</t>
         </is>
       </c>
       <c r="H21" s="95" t="inlineStr">
         <is>
-          <t>usecase v5 반영</t>
+          <t>usecase v6 반영</t>
         </is>
       </c>
     </row>
@@ -9750,7 +10428,7 @@
       </c>
       <c r="D22" s="95" t="inlineStr">
         <is>
-          <t>방식 확정 / 세부 미정</t>
+          <t>방식·토큰 정책 확정 / 약관 미정</t>
         </is>
       </c>
       <c r="E22" s="95" t="inlineStr">
@@ -9760,7 +10438,7 @@
       </c>
       <c r="F22" s="95" t="inlineStr">
         <is>
-          <t>토큰 만료·갱신·로그아웃 무효화 정책 미정.</t>
+          <t>접근 토큰 30분·갱신 토큰 14일·로그아웃 시 갱신 토큰 폐기·다중 기기·30일 유예 탈퇴 확정(v6). 약관·선택 동의·로그인 잠금 기준 미정.</t>
         </is>
       </c>
       <c r="G22" s="95" t="inlineStr">
@@ -9770,7 +10448,7 @@
       </c>
       <c r="H22" s="95" t="inlineStr">
         <is>
-          <t>usecase v3 반영</t>
+          <t>usecase v6 반영</t>
         </is>
       </c>
     </row>
@@ -9844,7 +10522,7 @@
       </c>
       <c r="F24" s="95" t="inlineStr">
         <is>
-          <t>프로토타입은 견본이며 정책 근거가 아님. 정정 항목 P-02~P-14 남음.</t>
+          <t>프로토타입은 견본이며 정책 근거가 아님. 정정 항목 P-02~P-15 남음. 최근 추가된 데모가 v6 결정과 맞는지는 아직 대조하지 않음.</t>
         </is>
       </c>
       <c r="G24" s="95" t="inlineStr">
@@ -9855,6 +10533,342 @@
       <c r="H24" s="95" t="inlineStr">
         <is>
           <t>usecase v5 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="44" customHeight="1" s="83">
+      <c r="A25" s="95" t="inlineStr">
+        <is>
+          <t>GAP-08</t>
+        </is>
+      </c>
+      <c r="B25" s="95" t="inlineStr">
+        <is>
+          <t>간트 8.2 / 기존 WBS 명시 없음</t>
+        </is>
+      </c>
+      <c r="C25" s="95" t="inlineStr">
+        <is>
+          <t>작품 검색(Elasticsearch)</t>
+        </is>
+      </c>
+      <c r="D25" s="95" t="inlineStr">
+        <is>
+          <t>검색 방식 확정 / 구축 작업 없음</t>
+        </is>
+      </c>
+      <c r="E25" s="95" t="inlineStr">
+        <is>
+          <t>UC-01, F-PUB-05. 공개 정보만 색인, 본문 검색 제외.</t>
+        </is>
+      </c>
+      <c r="F25" s="95" t="inlineStr">
+        <is>
+          <t>새 외부 구성요소. 한국어 분석 방식·색인 동기화(UC-28) 미정.</t>
+        </is>
+      </c>
+      <c r="G25" s="95" t="inlineStr">
+        <is>
+          <t>구현 전 팀 공유 후 담당·일정 합의.</t>
+        </is>
+      </c>
+      <c r="H25" s="95" t="inlineStr">
+        <is>
+          <t>usecase v6 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="44" customHeight="1" s="83">
+      <c r="A26" s="95" t="inlineStr">
+        <is>
+          <t>GAP-09</t>
+        </is>
+      </c>
+      <c r="B26" s="95" t="inlineStr">
+        <is>
+          <t>간트 8.5 / 기존 WBS 명시 없음</t>
+        </is>
+      </c>
+      <c r="C26" s="95" t="inlineStr">
+        <is>
+          <t>EPUB·이미지·일러스트</t>
+        </is>
+      </c>
+      <c r="D26" s="95" t="inlineStr">
+        <is>
+          <t>기능 확정 / 작업 없음</t>
+        </is>
+      </c>
+      <c r="E26" s="95" t="inlineStr">
+        <is>
+          <t>UC-03·10·11, F-WLD-09, F-WRT-12~14.</t>
+        </is>
+      </c>
+      <c r="F26" s="95" t="inlineStr">
+        <is>
+          <t>이미지 파일 저장 위치·대체 텍스트·일러스트 비용과 권리 귀속 미정. 이미지 생성 모델은 새 외부 호출.</t>
+        </is>
+      </c>
+      <c r="G26" s="95" t="inlineStr">
+        <is>
+          <t>저장소 방식 결정 후 작업 분해.</t>
+        </is>
+      </c>
+      <c r="H26" s="95" t="inlineStr">
+        <is>
+          <t>usecase v6 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="44" customHeight="1" s="83">
+      <c r="A27" s="95" t="inlineStr">
+        <is>
+          <t>GAP-10</t>
+        </is>
+      </c>
+      <c r="B27" s="95" t="inlineStr">
+        <is>
+          <t>간트 8.6 / 4.6 관련</t>
+        </is>
+      </c>
+      <c r="C27" s="95" t="inlineStr">
+        <is>
+          <t>유해 콘텐츠 1차 필터</t>
+        </is>
+      </c>
+      <c r="D27" s="95" t="inlineStr">
+        <is>
+          <t>방식 확정 / 작업 없음</t>
+        </is>
+      </c>
+      <c r="E27" s="95" t="inlineStr">
+        <is>
+          <t>UC-14·20, F-FBK-13, F-RPT-03. OpenAI 모더레이션 모델(AI Service 경유).</t>
+        </is>
+      </c>
+      <c r="F27" s="95" t="inlineStr">
+        <is>
+          <t>필터 대기 재검사 주기 미정. 숨긴 글은 삭제하지 않음.</t>
+        </is>
+      </c>
+      <c r="G27" s="95" t="inlineStr">
+        <is>
+          <t>4.6 피드백 에이전트와 분리해 작업 분해.</t>
+        </is>
+      </c>
+      <c r="H27" s="95" t="inlineStr">
+        <is>
+          <t>usecase v6 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="44" customHeight="1" s="83">
+      <c r="A28" s="95" t="inlineStr">
+        <is>
+          <t>GAP-11</t>
+        </is>
+      </c>
+      <c r="B28" s="95" t="inlineStr">
+        <is>
+          <t>간트 8.6·8.7 / 기존 WBS 명시 없음</t>
+        </is>
+      </c>
+      <c r="C28" s="95" t="inlineStr">
+        <is>
+          <t>검증 시뮬레이션·보상·크레딧 구조·속도 제한</t>
+        </is>
+      </c>
+      <c r="D28" s="95" t="inlineStr">
+        <is>
+          <t>규칙 확정 / 작업 없음</t>
+        </is>
+      </c>
+      <c r="E28" s="95" t="inlineStr">
+        <is>
+          <t>UC-09 A5·14·17, F-SIM-11, F-FBK-15, F-CRD-04·05.</t>
+        </is>
+      </c>
+      <c r="F28" s="95" t="inlineStr">
+        <is>
+          <t>보상 상한·플랜·환산 비율·속도 한도 값 미정. 현재는 테스트 크레딧만.</t>
+        </is>
+      </c>
+      <c r="G28" s="95" t="inlineStr">
+        <is>
+          <t>Core 크레딧 원장과 함께 작업 분해.</t>
+        </is>
+      </c>
+      <c r="H28" s="95" t="inlineStr">
+        <is>
+          <t>usecase v6 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="44" customHeight="1" s="83">
+      <c r="A29" s="95" t="inlineStr">
+        <is>
+          <t>GAP-12</t>
+        </is>
+      </c>
+      <c r="B29" s="95" t="inlineStr">
+        <is>
+          <t>간트 8.4 / 기존 WBS 명시 없음</t>
+        </is>
+      </c>
+      <c r="C29" s="95" t="inlineStr">
+        <is>
+          <t>알림함·정기 작업(Core 내장 스케줄러)</t>
+        </is>
+      </c>
+      <c r="D29" s="95" t="inlineStr">
+        <is>
+          <t>범위 확정 / 작업 없음</t>
+        </is>
+      </c>
+      <c r="E29" s="95" t="inlineStr">
+        <is>
+          <t>UC-27·28, F-NTF-01·02, F-JOB-01·02.</t>
+        </is>
+      </c>
+      <c r="F29" s="95" t="inlineStr">
+        <is>
+          <t>새 실행 계층(스케줄러). 작업별 주기·다중 서버 중복 실행 방지 미정.</t>
+        </is>
+      </c>
+      <c r="G29" s="95" t="inlineStr">
+        <is>
+          <t>구현 전 팀 공유 후 담당·일정 합의.</t>
+        </is>
+      </c>
+      <c r="H29" s="95" t="inlineStr">
+        <is>
+          <t>usecase v6 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="44" customHeight="1" s="83">
+      <c r="A30" s="95" t="inlineStr">
+        <is>
+          <t>GAP-13</t>
+        </is>
+      </c>
+      <c r="B30" s="95" t="inlineStr">
+        <is>
+          <t>간트 8.3·8.8 / 4.9·4.10~4.11 관련</t>
+        </is>
+      </c>
+      <c r="C30" s="95" t="inlineStr">
+        <is>
+          <t>LangChain·LangGraph 전환·Langfuse(Docker)·LLMOps</t>
+        </is>
+      </c>
+      <c r="D30" s="95" t="inlineStr">
+        <is>
+          <t>스택 확정 / 작업 없음</t>
+        </is>
+      </c>
+      <c r="E30" s="95" t="inlineStr">
+        <is>
+          <t>UC-26, F-LLM-01~05, backend/ai-service/AGENTS.md. 기존 openai-agents 의존성은 첫 AI 기능 구현 시 교체.</t>
+        </is>
+      </c>
+      <c r="F30" s="95" t="inlineStr">
+        <is>
+          <t>Langfuse에는 메타데이터만. 경고 기준·평가 세트 통과 기준·추적 보관 기간 미정.</t>
+        </is>
+      </c>
+      <c r="G30" s="95" t="inlineStr">
+        <is>
+          <t>첫 AI 기능 착수 시 의존성 교체를 PR·테스트로 진행.</t>
+        </is>
+      </c>
+      <c r="H30" s="95" t="inlineStr">
+        <is>
+          <t>usecase v6 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="44" customHeight="1" s="83">
+      <c r="A31" s="95" t="inlineStr">
+        <is>
+          <t>CHECK-07</t>
+        </is>
+      </c>
+      <c r="B31" s="95" t="inlineStr">
+        <is>
+          <t>3.2~3.7</t>
+        </is>
+      </c>
+      <c r="C31" s="95" t="inlineStr">
+        <is>
+          <t>피드백 라벨링·ML/DL 분류 모델 작업</t>
+        </is>
+      </c>
+      <c r="D31" s="95" t="inlineStr">
+        <is>
+          <t>재검토 필요 / 원본 보존</t>
+        </is>
+      </c>
+      <c r="E31" s="95" t="inlineStr">
+        <is>
+          <t>BR-15: 피드백 유형은 독자가 고르며 AI로 분류하지 않음(F-FBK-02).</t>
+        </is>
+      </c>
+      <c r="F31" s="95" t="inlineStr">
+        <is>
+          <t>런타임 분류 용도가 없어짐. 과정 산출물(ML/DL 학습결과서) 요구 여부 미확인. 담당자(문성호) 확인 전 삭제하지 않음.</t>
+        </is>
+      </c>
+      <c r="G31" s="95" t="inlineStr">
+        <is>
+          <t>용도 재정의 후보: 단순/스토리 오류 선택 보조 추천, UC-26 평가 세트 라벨. 담당자·팀 확인 후 결정.</t>
+        </is>
+      </c>
+      <c r="H31" s="95" t="inlineStr">
+        <is>
+          <t>usecase v6 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="44" customHeight="1" s="83">
+      <c r="A32" s="95" t="inlineStr">
+        <is>
+          <t>DOC-04</t>
+        </is>
+      </c>
+      <c r="B32" s="95" t="inlineStr">
+        <is>
+          <t>1.5 관련</t>
+        </is>
+      </c>
+      <c r="C32" s="95" t="inlineStr">
+        <is>
+          <t>요구사항 정의서 v6 반영</t>
+        </is>
+      </c>
+      <c r="D32" s="95" t="inlineStr">
+        <is>
+          <t>이번 반영</t>
+        </is>
+      </c>
+      <c r="E32" s="95" t="inlineStr">
+        <is>
+          <t>요구사항 116개(24개 추가, REQ15·REQ16 신설), F-FBK-02·03 재정의, 정리 기준 시트 갱신.</t>
+        </is>
+      </c>
+      <c r="F32" s="95" t="inlineStr">
+        <is>
+          <t>새 ID에 담당·일정은 부여하지 않음.</t>
+        </is>
+      </c>
+      <c r="G32" s="95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" s="95" t="inlineStr">
+        <is>
+          <t>usecase v6 반영</t>
         </is>
       </c>
     </row>

--- a/docs/SKN34-final-4Team_WBS.xlsx
+++ b/docs/SKN34-final-4Team_WBS.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="갠트 차트 템플릿" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발현황" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="갠트 차트 템플릿" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="개발현황" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'개발현황'!$A$3:$H$20</definedName>
@@ -989,7 +989,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ86"/>
+  <dimension ref="A1:BQ87"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1" outlineLevelRow="1"/>
   <cols>
     <col width="4.25" customWidth="1" style="83" min="1" max="1"/>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="C78" s="56" t="inlineStr">
         <is>
-          <t>v6 추가 작업 (담당·일정 미정)</t>
+          <t>v6·v7 추가 작업 (담당·일정 미정)</t>
         </is>
       </c>
       <c r="D78" s="56" t="n"/>
@@ -8069,7 +8069,7 @@
       </c>
       <c r="C80" s="95" t="inlineStr">
         <is>
-          <t>Elasticsearch 검색 구축·색인 동기화</t>
+          <t>Elasticsearch 검색 구축·색인 동기화 (MVP 제외, MVP는 DB 검색)</t>
         </is>
       </c>
       <c r="D80" s="95" t="n"/>
@@ -8297,7 +8297,7 @@
       </c>
       <c r="C83" s="95" t="inlineStr">
         <is>
-          <t>이미지 저장소·EPUB 가져오기/내보내기·일러스트 생성</t>
+          <t>이미지 저장소(MinIO)·EPUB 가져오기/내보내기 (일러스트 생성은 MVP 제외)</t>
         </is>
       </c>
       <c r="D83" s="95" t="n"/>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="C85" s="95" t="inlineStr">
         <is>
-          <t>크레딧 구조(구독·후차감)·요청 속도 제한</t>
+          <t>크레딧 구조(예약·후차감, 구독은 MVP 제외)·요청 속도 제한</t>
         </is>
       </c>
       <c r="D85" s="95" t="n"/>
@@ -8525,7 +8525,7 @@
       </c>
       <c r="C86" s="95" t="inlineStr">
         <is>
-          <t>LLMOps 평가 세트·AI 운영 화면</t>
+          <t>LLMOps 평가 세트·AI 운영 화면 (평가 세트·표본 검사는 MVP 제외)</t>
         </is>
       </c>
       <c r="D86" s="95" t="n"/>
@@ -8592,7 +8592,82 @@
       <c r="BP86" s="79" t="n"/>
       <c r="BQ86" s="65" t="n"/>
     </row>
-    <row r="87" ht="15.75" customHeight="1" s="83"/>
+    <row r="87" ht="17.25" customHeight="1" s="83">
+      <c r="A87" s="65" t="n"/>
+      <c r="B87" s="66" t="inlineStr">
+        <is>
+          <t>8.9</t>
+        </is>
+      </c>
+      <c r="C87" s="95" t="inlineStr">
+        <is>
+          <t>SMTP 인증 메일 발송·로컬 Mailpit 구성</t>
+        </is>
+      </c>
+      <c r="D87" s="95" t="n"/>
+      <c r="E87" s="68" t="n"/>
+      <c r="F87" s="68" t="n"/>
+      <c r="G87" s="69" t="n"/>
+      <c r="H87" s="70" t="n"/>
+      <c r="I87" s="71" t="n"/>
+      <c r="J87" s="72" t="n"/>
+      <c r="K87" s="73" t="n"/>
+      <c r="L87" s="73" t="n"/>
+      <c r="P87" s="75" t="n"/>
+      <c r="Q87" s="75" t="n"/>
+      <c r="R87" s="75" t="n"/>
+      <c r="S87" s="73" t="n"/>
+      <c r="T87" s="73" t="n"/>
+      <c r="U87" s="73" t="n"/>
+      <c r="V87" s="73" t="n"/>
+      <c r="W87" s="73" t="n"/>
+      <c r="X87" s="73" t="n"/>
+      <c r="Y87" s="73" t="n"/>
+      <c r="Z87" s="73" t="n"/>
+      <c r="AA87" s="73" t="n"/>
+      <c r="AB87" s="73" t="n"/>
+      <c r="AC87" s="76" t="n"/>
+      <c r="AD87" s="76" t="n"/>
+      <c r="AE87" s="76" t="n"/>
+      <c r="AF87" s="76" t="n"/>
+      <c r="AG87" s="76" t="n"/>
+      <c r="AH87" s="73" t="n"/>
+      <c r="AI87" s="73" t="n"/>
+      <c r="AJ87" s="73" t="n"/>
+      <c r="AK87" s="73" t="n"/>
+      <c r="AL87" s="73" t="n"/>
+      <c r="AM87" s="73" t="n"/>
+      <c r="AN87" s="73" t="n"/>
+      <c r="AO87" s="73" t="n"/>
+      <c r="AP87" s="73" t="n"/>
+      <c r="AQ87" s="73" t="n"/>
+      <c r="AR87" s="77" t="n"/>
+      <c r="AS87" s="77" t="n"/>
+      <c r="AT87" s="77" t="n"/>
+      <c r="AU87" s="77" t="n"/>
+      <c r="AV87" s="77" t="n"/>
+      <c r="AW87" s="73" t="n"/>
+      <c r="AX87" s="73" t="n"/>
+      <c r="AY87" s="73" t="n"/>
+      <c r="AZ87" s="73" t="n"/>
+      <c r="BA87" s="73" t="n"/>
+      <c r="BB87" s="73" t="n"/>
+      <c r="BC87" s="73" t="n"/>
+      <c r="BD87" s="73" t="n"/>
+      <c r="BE87" s="73" t="n"/>
+      <c r="BF87" s="73" t="n"/>
+      <c r="BG87" s="78" t="n"/>
+      <c r="BH87" s="78" t="n"/>
+      <c r="BI87" s="78" t="n"/>
+      <c r="BJ87" s="78" t="n"/>
+      <c r="BK87" s="78" t="n"/>
+      <c r="BL87" s="73" t="n"/>
+      <c r="BM87" s="73" t="n"/>
+      <c r="BN87" s="73" t="n"/>
+      <c r="BO87" s="73" t="n"/>
+      <c r="BP87" s="79" t="n"/>
+      <c r="BQ87" s="65" t="n"/>
+    </row>
     <row r="88" ht="15.75" customHeight="1" s="83"/>
     <row r="89" ht="15.75" customHeight="1" s="83"/>
     <row r="90" ht="15.75" customHeight="1" s="83"/>
@@ -9571,7 +9646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="24"/>
   <cols>
     <col width="17" customWidth="1" style="83" min="1" max="1"/>
@@ -9601,7 +9676,7 @@
     <row r="2" ht="42" customHeight="1" s="83">
       <c r="A2" s="95" t="inlineStr">
         <is>
-          <t>2026-10-27 저장소 확인 기준, 2026-10-28 유스케이스 v6 결정 반영. 원본 간트의 담당자·일정·기간·완료율은 그대로 보존했습니다. 아래 현황은 실행 재검증이나 팀 외부 작업 확인을 대신하지 않습니다.</t>
+          <t>2026-10-27 저장소 확인 기준, 2026-10-28 유스케이스 v6 결정 반영. 원본 간트의 담당자·일정·기간·완료율은 그대로 보존했습니다. 아래 현황은 실행 재검증이나 팀 외부 작업 확인을 대신하지 않습니다. 2026-10-28 유스케이스 v7 결정 반영.</t>
         </is>
       </c>
       <c r="B2" s="94" t="n"/>
@@ -9756,12 +9831,12 @@
       </c>
       <c r="D6" s="95" t="inlineStr">
         <is>
-          <t>v6 작성 / 일부 정책 미확정</t>
+          <t>v7 작성 / 일부 정책 미확정</t>
         </is>
       </c>
       <c r="E6" s="95" t="inlineStr">
         <is>
-          <t>docs/usecase.md v6, docs/usecase-spec/UC-01~28.md. Fork·원고 입력(EPUB·이미지·일러스트)·계정·피드백(BR-15)·크레딧(후차감·구독)·자율 연재·권리 신고·탐색 정책 확정, UC-26~28 추가, UC-25 채택(MVP 제외).</t>
+          <t>docs/usecase.md v7, docs/usecase-spec/UC-01~28.md. Fork·원고 입력(EPUB·이미지·일러스트)·계정·피드백(BR-15)·크레딧(후차감·구독)·자율 연재·권리 신고·탐색 정책 확정, UC-26~28 추가, UC-25 채택(MVP 제외). v7: MVP 범위·공개 용어 3분리·저장 경계·Fork·표기 오류·크레딧 예약·KST·인증 메일·MinIO 결정, 문서 불일치 8건 정리.</t>
         </is>
       </c>
       <c r="F6" s="95" t="inlineStr">
@@ -9776,7 +9851,7 @@
       </c>
       <c r="H6" s="95" t="inlineStr">
         <is>
-          <t>usecase v6 반영</t>
+          <t>usecase v7 반영</t>
         </is>
       </c>
     </row>
@@ -10228,7 +10303,7 @@
       </c>
       <c r="F17" s="95" t="inlineStr">
         <is>
-          <t>가격·플랜·토큰 환산 비율 미정. 자율 연재는 Core 내장 스케줄러로 확정했지만 구현 작업이 없음. 결제 연동은 승인하지 않음.</t>
+          <t>가격·플랜·토큰 환산 비율 미정. 자율 연재는 Core 내장 스케줄러로 확정했지만 구현 작업이 없음. 결제 연동은 승인하지 않음. UC-19 저장 공간은 MVP 제외(v7).</t>
         </is>
       </c>
       <c r="G17" s="95" t="inlineStr">
@@ -10391,7 +10466,7 @@
       </c>
       <c r="E21" s="95" t="inlineStr">
         <is>
-          <t>usecase.md §6.2: 세계관·인물관계도는 Gitea로 변경 이력 관리(HEAD 위 새 버전, 덮어쓰기·머지 없음), 회차 원고는 DB. 작품 Fork는 분기 시점 버전 참조, 세계관 Fork는 출처 기록.</t>
+          <t>usecase.md §6.2(v7): 세계관 설정 값·인물 기본 정보는 세계관별 Gitea 저장소로 변경 이력 관리(HEAD 위 새 버전, 덮어쓰기·머지 없음), 회차 원고·작품별 회차 기록은 DB. 작품 Fork는 커밋 ID와 작품별 회차 기록 사본으로 고정, 세계관 Fork는 출처 기록.</t>
         </is>
       </c>
       <c r="F21" s="95" t="inlineStr">
@@ -10406,7 +10481,7 @@
       </c>
       <c r="H21" s="95" t="inlineStr">
         <is>
-          <t>usecase v6 반영</t>
+          <t>usecase v7 반영</t>
         </is>
       </c>
     </row>
@@ -10438,17 +10513,17 @@
       </c>
       <c r="F22" s="95" t="inlineStr">
         <is>
-          <t>접근 토큰 30분·갱신 토큰 14일·로그아웃 시 갱신 토큰 폐기·다중 기기·30일 유예 탈퇴 확정(v6). 약관·선택 동의·로그인 잠금 기준 미정.</t>
+          <t>접근 토큰 30분·갱신 토큰 14일·로그아웃 시 갱신 토큰 폐기·다중 기기·30일 유예 탈퇴 확정(v6). 약관·선택 동의·로그인 잠금 기준 미정. 인증 메일은 SMTP·개발 환경 로컬 Mailpit(v7 확정).</t>
         </is>
       </c>
       <c r="G22" s="95" t="inlineStr">
         <is>
-          <t>5.7에서 토큰 정책 확정 후 구현.</t>
+          <t>5.7에서 구현. 메일 발송·Mailpit 구성은 간트 8.9.</t>
         </is>
       </c>
       <c r="H22" s="95" t="inlineStr">
         <is>
-          <t>usecase v6 반영</t>
+          <t>usecase v7 반영</t>
         </is>
       </c>
     </row>
@@ -10554,7 +10629,7 @@
       </c>
       <c r="D25" s="95" t="inlineStr">
         <is>
-          <t>검색 방식 확정 / 구축 작업 없음</t>
+          <t>검색 방식 확정 / MVP 제외</t>
         </is>
       </c>
       <c r="E25" s="95" t="inlineStr">
@@ -10564,7 +10639,7 @@
       </c>
       <c r="F25" s="95" t="inlineStr">
         <is>
-          <t>새 외부 구성요소. 한국어 분석 방식·색인 동기화(UC-28) 미정.</t>
+          <t>새 외부 구성요소. 한국어 분석 방식·색인 동기화(UC-28) 미정. MVP는 DB 검색으로 제공(v7).</t>
         </is>
       </c>
       <c r="G25" s="95" t="inlineStr">
@@ -10574,7 +10649,7 @@
       </c>
       <c r="H25" s="95" t="inlineStr">
         <is>
-          <t>usecase v6 반영</t>
+          <t>usecase v7 반영</t>
         </is>
       </c>
     </row>
@@ -10606,17 +10681,17 @@
       </c>
       <c r="F26" s="95" t="inlineStr">
         <is>
-          <t>이미지 파일 저장 위치·대체 텍스트·일러스트 비용과 권리 귀속 미정. 이미지 생성 모델은 새 외부 호출.</t>
+          <t>이미지는 MinIO에 저장(v7 확정, 새 구성요소). 대체 텍스트 입력 방식 미정. 일러스트 생성은 MVP 제외이며 비용·권리 귀속 미정.</t>
         </is>
       </c>
       <c r="G26" s="95" t="inlineStr">
         <is>
-          <t>저장소 방식 결정 후 작업 분해.</t>
+          <t>MinIO 구성 팀 공유 후 작업 분해.</t>
         </is>
       </c>
       <c r="H26" s="95" t="inlineStr">
         <is>
-          <t>usecase v6 반영</t>
+          <t>usecase v7 반영</t>
         </is>
       </c>
     </row>
@@ -10690,7 +10765,7 @@
       </c>
       <c r="F28" s="95" t="inlineStr">
         <is>
-          <t>보상 상한·플랜·환산 비율·속도 한도 값 미정. 현재는 테스트 크레딧만.</t>
+          <t>크레딧 예약 후 정산·소멸 임박 순 차감·매월 1일 KST 초기화·환산 비율 설정값(v7 확정). 보상 상한·플랜·환산 비율 값·속도 한도 값 미정. 구독·추가 구매는 MVP 제외, 테스트 크레딧만.</t>
         </is>
       </c>
       <c r="G28" s="95" t="inlineStr">
@@ -10700,7 +10775,7 @@
       </c>
       <c r="H28" s="95" t="inlineStr">
         <is>
-          <t>usecase v6 반영</t>
+          <t>usecase v7 반영</t>
         </is>
       </c>
     </row>
@@ -10732,7 +10807,7 @@
       </c>
       <c r="F29" s="95" t="inlineStr">
         <is>
-          <t>새 실행 계층(스케줄러). 작업별 주기·다중 서버 중복 실행 방지 미정.</t>
+          <t>새 실행 계층(스케줄러). KST·밀린 작업 처리 규칙 확정(v7). 작업별 주기·다중 서버 중복 실행 방지 미정.</t>
         </is>
       </c>
       <c r="G29" s="95" t="inlineStr">
@@ -10742,7 +10817,7 @@
       </c>
       <c r="H29" s="95" t="inlineStr">
         <is>
-          <t>usecase v6 반영</t>
+          <t>usecase v7 반영</t>
         </is>
       </c>
     </row>
@@ -10774,7 +10849,7 @@
       </c>
       <c r="F30" s="95" t="inlineStr">
         <is>
-          <t>Langfuse에는 메타데이터만. 경고 기준·평가 세트 통과 기준·추적 보관 기간 미정.</t>
+          <t>Langfuse에는 메타데이터만. 경고 기준·평가 세트 통과 기준·추적 보관 기간 미정. MVP는 Langfuse 추적만, 평가 세트·표본 검사는 제외(v7).</t>
         </is>
       </c>
       <c r="G30" s="95" t="inlineStr">
@@ -10784,7 +10859,7 @@
       </c>
       <c r="H30" s="95" t="inlineStr">
         <is>
-          <t>usecase v6 반영</t>
+          <t>usecase v7 반영</t>
         </is>
       </c>
     </row>
@@ -10869,6 +10944,48 @@
       <c r="H32" s="95" t="inlineStr">
         <is>
           <t>usecase v6 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="44" customHeight="1" s="83">
+      <c r="A33" s="95" t="inlineStr">
+        <is>
+          <t>DOC-05</t>
+        </is>
+      </c>
+      <c r="B33" s="95" t="inlineStr">
+        <is>
+          <t>1.5·1.6 관련</t>
+        </is>
+      </c>
+      <c r="C33" s="95" t="inlineStr">
+        <is>
+          <t>유스케이스 v7 검증·결정 반영</t>
+        </is>
+      </c>
+      <c r="D33" s="95" t="inlineStr">
+        <is>
+          <t>이번 반영 / 기능 개발 아님</t>
+        </is>
+      </c>
+      <c r="E33" s="95" t="inlineStr">
+        <is>
+          <t>문서 불일치 8건 정리, 결정 11건(MVP 범위·공개 용어·Fork 세계관 공개 조건·저장 경계·원작 삭제 시 Fork 본문·표기 오류 자동 처리 경계·Fork 세계관 연결 수·밀린 정기 작업·크레딧 예약·KST·인증 메일·MinIO) 반영. 요구사항 ID 추가 없음. 간트 8.9 추가.</t>
+        </is>
+      </c>
+      <c r="F33" s="95" t="inlineStr">
+        <is>
+          <t>MinIO·Mailpit은 새 구성요소로 구현 전 팀 공유. architecture.md·prototype-alignment.md는 미반영.</t>
+        </is>
+      </c>
+      <c r="G33" s="95" t="inlineStr">
+        <is>
+          <t>간트 8.9 담당·일정 합의, 남은 미정(환산 비율 값 등) 합의.</t>
+        </is>
+      </c>
+      <c r="H33" s="95" t="inlineStr">
+        <is>
+          <t>usecase v7 반영</t>
         </is>
       </c>
     </row>

--- a/docs/SKN34-final-4Team_WBS.xlsx
+++ b/docs/SKN34-final-4Team_WBS.xlsx
@@ -10765,7 +10765,7 @@
       </c>
       <c r="F28" s="95" t="inlineStr">
         <is>
-          <t>크레딧 예약 후 정산·소멸 임박 순 차감·매월 1일 KST 초기화·환산 비율 설정값(v7 확정). 보상 상한·플랜·환산 비율 값·속도 한도 값 미정. 구독·추가 구매는 MVP 제외, 테스트 크레딧만.</t>
+          <t>크레딧 예약 후 정산·소멸 임박 순 차감·매월 1일 KST 초기화·환산 비율 설정값(v7 확정). 보상 상한·플랜·환산 비율 값·속도 한도 값 미정. 구독·추가 구매는 MVP 제외, 가입 체험·보상·이벤트 크레딧만(추가 지급은 이벤트 크레딧).</t>
         </is>
       </c>
       <c r="G28" s="95" t="inlineStr">
